--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45917.4375</v>
+        <v>45917.39583333334</v>
       </c>
     </row>
     <row r="3">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45917.45833333334</v>
+        <v>45917.4375</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45917.47916666666</v>
+        <v>45917.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45917.48958333334</v>
+        <v>45917.47916666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.48958333334</v>
       </c>
     </row>
     <row r="11">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.4</v>
+        <v>3.15</v>
       </c>
       <c r="M43" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>7.6</v>
+        <v>2.25</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.15</v>
+        <v>1.85</v>
       </c>
       <c r="M44" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N44" t="n">
-        <v>2.25</v>
+        <v>4.05</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="M45" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="N45" t="n">
-        <v>4.05</v>
+        <v>7.6</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK51"/>
+  <dimension ref="A1:AK50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45917.47916666666</v>
+        <v>45917.46875</v>
       </c>
     </row>
     <row r="7">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45917.48958333334</v>
+        <v>45917.47916666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.48958333334</v>
       </c>
     </row>
     <row r="12">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.5</v>
       </c>
     </row>
     <row r="17">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N22" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>3.57</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4830,10 +4830,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5088,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,10 +5346,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5825,17 +5825,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45917.64583333334</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="43">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="M44" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M45" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="N45" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>2.25</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.75</v>
+        <v>3.76</v>
       </c>
       <c r="M46" t="n">
-        <v>3.65</v>
+        <v>3.79</v>
       </c>
       <c r="N46" t="n">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M47" t="n">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="N47" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6599,65 +6599,65 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45917.85416666666</v>
+        <v>45917.875</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6765,16 +6765,16 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45917.875</v>
+        <v>45917.89583333334</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6857,17 +6857,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="M50" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="N50" t="n">
-        <v>3.22</v>
+        <v>2.5</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6894,16 +6894,16 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6940,135 +6940,6 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45917.89583333334</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" s="3" t="n">
         <v>45917.9375</v>
       </c>
     </row>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4830,10 +4830,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4959,10 +4959,10 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5088,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="M37" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="N37" t="n">
-        <v>7.5</v>
+        <v>3.05</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,16 +5217,16 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="M38" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,10 +5346,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="X38" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N44" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.33</v>
+        <v>3.76</v>
       </c>
       <c r="M45" t="n">
-        <v>5.2</v>
+        <v>3.79</v>
       </c>
       <c r="N45" t="n">
-        <v>7.9</v>
+        <v>1.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.76</v>
+        <v>1.64</v>
       </c>
       <c r="M46" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>6.8</v>
+        <v>3.57</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.57</v>
+        <v>6.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="M37" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>7.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,16 +5217,16 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="M38" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="N38" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,10 +5346,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="X38" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.44</v>
+        <v>3.3</v>
       </c>
       <c r="M39" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="N39" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,16 +5475,16 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.33</v>
+        <v>3.76</v>
       </c>
       <c r="M43" t="n">
-        <v>5.2</v>
+        <v>3.79</v>
       </c>
       <c r="N43" t="n">
-        <v>7.9</v>
+        <v>1.85</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.76</v>
+        <v>1.64</v>
       </c>
       <c r="M45" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK50"/>
+  <dimension ref="A1:AK56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,65 +2342,65 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.5</v>
       </c>
     </row>
     <row r="18">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45917.5625</v>
+        <v>45917.54166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45917.57291666666</v>
+        <v>45917.5625</v>
       </c>
     </row>
     <row r="23">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.57291666666</v>
       </c>
     </row>
     <row r="25">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3632,65 +3632,65 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3761,65 +3761,65 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>8.74</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4959,10 +4959,10 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.54</v>
+        <v>2.23</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,10 +5346,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.3</v>
+        <v>1.44</v>
       </c>
       <c r="M39" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,16 +5475,16 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5733,10 +5733,10 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5862,10 +5862,10 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.76</v>
+        <v>2.15</v>
       </c>
       <c r="M43" t="n">
-        <v>3.79</v>
+        <v>2.8</v>
       </c>
       <c r="N43" t="n">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5991,16 +5991,16 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.64</v>
+        <v>1.23</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="N45" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="47">
@@ -6433,27 +6433,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45917.8125</v>
+        <v>45917.64583333334</v>
       </c>
     </row>
     <row r="48">
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45917.875</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="49">
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6765,16 +6765,16 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45917.89583333334</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,126 +6820,900 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Inter Milan</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3" t="n">
+        <v>45917.66666666666</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3" t="n">
+        <v>45917.66666666666</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Bayern München</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3" t="n">
+        <v>45917.66666666666</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N53" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3" t="n">
+        <v>45917.8125</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC II</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="3" t="n">
+        <v>45917.875</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="3" t="n">
+        <v>45917.89583333334</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Real Salt Lake</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="L56" t="n">
         <v>2.7</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M56" t="n">
         <v>3.6</v>
       </c>
-      <c r="N50" t="n">
+      <c r="N56" t="n">
         <v>2.5</v>
       </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
         <v>1.82</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="Z56" t="n">
         <v>1.98</v>
       </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" s="3" t="n">
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="3" t="n">
         <v>45917.9375</v>
       </c>
     </row>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK56"/>
+  <dimension ref="A1:AK54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,65 +2342,65 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>6.8</v>
+        <v>3.57</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.57</v>
+        <v>6.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3761,65 +3761,65 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.31</v>
+        <v>2.33</v>
       </c>
       <c r="M26" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>8.74</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.9</v>
+        <v>2.04</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,16 +5217,16 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="M39" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="N39" t="n">
-        <v>7.5</v>
+        <v>3.05</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,16 +5475,16 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5604,10 +5604,10 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="M41" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>3.05</v>
+        <v>7.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5733,16 +5733,16 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5862,10 +5862,10 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5991,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.64583333334</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45917.64583333334</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="48">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.76</v>
+        <v>1.64</v>
       </c>
       <c r="M50" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6949,27 +6949,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="M51" t="n">
-        <v>5.2</v>
+        <v>3.51</v>
       </c>
       <c r="N51" t="n">
-        <v>7.9</v>
+        <v>5.1</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,16 +7029,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.8125</v>
       </c>
     </row>
     <row r="52">
@@ -7078,27 +7078,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,16 +7158,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.875</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="M53" t="n">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="N53" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7281,16 +7281,16 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45917.8125</v>
+        <v>45917.89583333334</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7456,264 +7456,6 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45917.875</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>River Plate</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" s="3" t="n">
-        <v>45917.89583333334</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" s="3" t="n">
         <v>45917.9375</v>
       </c>
     </row>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.14</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>13</v>
+        <v>2.05</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.57</v>
+        <v>6.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>6.8</v>
+        <v>3.57</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3632,17 +3632,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3761,17 +3761,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="N41" t="n">
-        <v>7.5</v>
+        <v>3.05</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5733,16 +5733,16 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="N47" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N50" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,16 +6900,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.14</v>
+        <v>3.1</v>
       </c>
       <c r="M13" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>13</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,65 +2471,65 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.69</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.82</v>
+        <v>2.23</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="M37" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="N37" t="n">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,16 +5217,16 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5604,10 +5604,10 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="M41" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N41" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5733,10 +5733,10 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="X41" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5862,10 +5862,10 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6003,10 +6003,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="M47" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="N47" t="n">
-        <v>7.9</v>
+        <v>4.2</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.76</v>
+        <v>1.64</v>
       </c>
       <c r="M48" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="N49" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,16 +6900,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.14</v>
+        <v>3.1</v>
       </c>
       <c r="M12" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,65 +4406,65 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="M37" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="N37" t="n">
-        <v>7.5</v>
+        <v>3.05</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,16 +5217,16 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,10 +5346,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.3</v>
+        <v>1.44</v>
       </c>
       <c r="M41" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5733,16 +5733,16 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="M42" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5862,10 +5862,10 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="X42" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.76</v>
+        <v>1.69</v>
       </c>
       <c r="M46" t="n">
-        <v>3.79</v>
+        <v>4.2</v>
       </c>
       <c r="N46" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.33</v>
+        <v>3.76</v>
       </c>
       <c r="M49" t="n">
-        <v>5.2</v>
+        <v>3.79</v>
       </c>
       <c r="N49" t="n">
-        <v>7.9</v>
+        <v>1.85</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,16 +6900,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,65 +2213,65 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,17 +2600,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,10 +5217,10 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,10 +5346,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5604,10 +5604,10 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.69</v>
+        <v>3.76</v>
       </c>
       <c r="M46" t="n">
-        <v>4.2</v>
+        <v>3.79</v>
       </c>
       <c r="N46" t="n">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.76</v>
+        <v>1.69</v>
       </c>
       <c r="M49" t="n">
-        <v>3.79</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="M50" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>7.9</v>
+        <v>4.7</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,16 +6900,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK54"/>
+  <dimension ref="A1:AK56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,65 +2213,65 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>6.8</v>
+        <v>3.57</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.57</v>
+        <v>6.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>8.74</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45917.58333333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.33</v>
+        <v>3.59</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="M40" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N40" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5604,10 +5604,10 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="X40" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="N42" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5862,10 +5862,10 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="X42" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6003,10 +6003,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45917.64583333334</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.64583333334</v>
       </c>
     </row>
     <row r="48">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="N49" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N50" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,16 +6900,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6949,27 +6949,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="M51" t="n">
-        <v>3.51</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45917.8125</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="52">
@@ -7078,27 +7078,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45917.875</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="M53" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="N53" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7281,16 +7281,16 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45917.89583333334</v>
+        <v>45917.8125</v>
       </c>
     </row>
     <row r="54">
@@ -7336,126 +7336,384 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC II</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="3" t="n">
+        <v>45917.875</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="3" t="n">
+        <v>45917.89583333334</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Real Salt Lake</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L54" t="n">
+      <c r="L56" t="n">
         <v>2.7</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M56" t="n">
         <v>3.6</v>
       </c>
-      <c r="N54" t="n">
+      <c r="N56" t="n">
         <v>2.5</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O56" t="n">
         <v>3.25</v>
       </c>
-      <c r="P54" t="n">
+      <c r="P56" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q56" t="n">
         <v>3.15</v>
       </c>
-      <c r="R54" t="n">
+      <c r="R56" t="n">
         <v>1.35</v>
       </c>
-      <c r="S54" t="n">
+      <c r="S56" t="n">
         <v>3</v>
       </c>
-      <c r="T54" t="n">
+      <c r="T56" t="n">
         <v>2.7</v>
       </c>
-      <c r="U54" t="n">
+      <c r="U56" t="n">
         <v>1.46</v>
       </c>
-      <c r="V54" t="n">
+      <c r="V56" t="n">
         <v>1.02</v>
       </c>
-      <c r="W54" t="n">
+      <c r="W56" t="n">
         <v>1.25</v>
       </c>
-      <c r="X54" t="n">
+      <c r="X56" t="n">
         <v>3.85</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="Y56" t="n">
         <v>1.82</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="Z56" t="n">
         <v>1.98</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AA56" t="n">
         <v>3.05</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AB56" t="n">
         <v>1.37</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AC56" t="n">
         <v>1.72</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AD56" t="n">
         <v>2.14</v>
       </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AH56" t="n">
         <v>1.46</v>
       </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" s="3" t="n">
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="3" t="n">
         <v>45917.9375</v>
       </c>
     </row>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK56"/>
+  <dimension ref="A1:AK60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45917.48958333334</v>
+        <v>45917.47916666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.47916666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.47916666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.47916666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.48958333334</v>
       </c>
     </row>
     <row r="16">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,17 +2600,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,65 +2729,65 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.19</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X18" t="n">
         <v>3.25</v>
       </c>
-      <c r="N18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,17 +2858,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.5</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.5</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45917.5625</v>
+        <v>45917.5</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45917.5625</v>
+        <v>45917.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45917.57291666666</v>
+        <v>45917.54166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45917.57291666666</v>
+        <v>45917.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.5625</v>
       </c>
     </row>
     <row r="26">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>8.74</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,19 +3832,19 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.5625</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.75</v>
+        <v>3.57</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.57291666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.57291666666</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>8.74</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5604,10 +5604,10 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="M42" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5862,16 +5862,16 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.23</v>
+        <v>3.3</v>
       </c>
       <c r="M45" t="n">
-        <v>6.4</v>
+        <v>2.85</v>
       </c>
       <c r="N45" t="n">
-        <v>11</v>
+        <v>2.3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6249,10 +6249,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6378,10 +6378,10 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45917.64583333334</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6636,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.69</v>
+        <v>1.23</v>
       </c>
       <c r="M50" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="N50" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,16 +6900,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.64583333334</v>
       </c>
     </row>
     <row r="52">
@@ -7207,27 +7207,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45917.8125</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="54">
@@ -7336,27 +7336,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45917.875</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="55">
@@ -7465,27 +7465,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="M55" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N55" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7539,22 +7539,22 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.53</v>
+        <v>2.39</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45917.89583333334</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="56">
@@ -7594,126 +7594,642 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M56" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N56" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="3" t="n">
+        <v>45917.66666666666</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N57" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="3" t="n">
+        <v>45917.8125</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC II</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3" t="n">
+        <v>45917.875</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X59" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="3" t="n">
+        <v>45917.89583333334</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Real Salt Lake</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L56" t="n">
+      <c r="L60" t="n">
         <v>2.7</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M60" t="n">
         <v>3.6</v>
       </c>
-      <c r="N56" t="n">
+      <c r="N60" t="n">
         <v>2.5</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O60" t="n">
         <v>3.25</v>
       </c>
-      <c r="P56" t="n">
+      <c r="P60" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="Q60" t="n">
         <v>3.15</v>
       </c>
-      <c r="R56" t="n">
+      <c r="R60" t="n">
         <v>1.35</v>
       </c>
-      <c r="S56" t="n">
+      <c r="S60" t="n">
         <v>3</v>
       </c>
-      <c r="T56" t="n">
+      <c r="T60" t="n">
         <v>2.7</v>
       </c>
-      <c r="U56" t="n">
+      <c r="U60" t="n">
         <v>1.46</v>
       </c>
-      <c r="V56" t="n">
+      <c r="V60" t="n">
         <v>1.02</v>
       </c>
-      <c r="W56" t="n">
+      <c r="W60" t="n">
         <v>1.25</v>
       </c>
-      <c r="X56" t="n">
+      <c r="X60" t="n">
         <v>3.85</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Y60" t="n">
         <v>1.82</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="Z60" t="n">
         <v>1.98</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AA60" t="n">
         <v>3.05</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AB60" t="n">
         <v>1.37</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AC60" t="n">
         <v>1.72</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AD60" t="n">
         <v>2.14</v>
       </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AH60" t="n">
         <v>1.46</v>
       </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" s="3" t="n">
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="3" t="n">
         <v>45917.9375</v>
       </c>
     </row>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK60"/>
+  <dimension ref="A1:AK61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,17 +2600,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,65 +2729,65 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,17 +2858,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,65 +2987,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,65 +4406,65 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>8.74</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>8.74</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6120,10 +6120,10 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="M46" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6378,16 +6378,16 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6507,10 +6507,10 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6636,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,16 +7287,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="N54" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,16 +7545,16 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="M56" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>7.9</v>
+        <v>4.7</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,16 +7674,16 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45917.875</v>
+        <v>45917.85416666666</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8055,16 +8055,16 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45917.89583333334</v>
+        <v>45917.875</v>
       </c>
     </row>
     <row r="60">
@@ -8110,126 +8110,255 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X60" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="3" t="n">
+        <v>45917.89583333334</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Real Salt Lake</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L60" t="n">
+      <c r="L61" t="n">
         <v>2.7</v>
       </c>
-      <c r="M60" t="n">
+      <c r="M61" t="n">
         <v>3.6</v>
       </c>
-      <c r="N60" t="n">
+      <c r="N61" t="n">
         <v>2.5</v>
       </c>
-      <c r="O60" t="n">
+      <c r="O61" t="n">
         <v>3.25</v>
       </c>
-      <c r="P60" t="n">
+      <c r="P61" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="Q61" t="n">
         <v>3.15</v>
       </c>
-      <c r="R60" t="n">
+      <c r="R61" t="n">
         <v>1.35</v>
       </c>
-      <c r="S60" t="n">
+      <c r="S61" t="n">
         <v>3</v>
       </c>
-      <c r="T60" t="n">
+      <c r="T61" t="n">
         <v>2.7</v>
       </c>
-      <c r="U60" t="n">
+      <c r="U61" t="n">
         <v>1.46</v>
       </c>
-      <c r="V60" t="n">
+      <c r="V61" t="n">
         <v>1.02</v>
       </c>
-      <c r="W60" t="n">
+      <c r="W61" t="n">
         <v>1.25</v>
       </c>
-      <c r="X60" t="n">
+      <c r="X61" t="n">
         <v>3.85</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="Y61" t="n">
         <v>1.82</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="Z61" t="n">
         <v>1.98</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AA61" t="n">
         <v>3.05</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AB61" t="n">
         <v>1.37</v>
       </c>
-      <c r="AC60" t="n">
+      <c r="AC61" t="n">
         <v>1.72</v>
       </c>
-      <c r="AD60" t="n">
+      <c r="AD61" t="n">
         <v>2.14</v>
       </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG60" t="n">
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH60" t="n">
+      <c r="AH61" t="n">
         <v>1.46</v>
       </c>
-      <c r="AI60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK60" s="3" t="n">
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3" t="n">
         <v>45917.9375</v>
       </c>
     </row>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.14</v>
+        <v>2.99</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>13</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,65 +2987,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.57</v>
+        <v>6.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>6.8</v>
+        <v>3.57</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4277,65 +4277,65 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.59</v>
+        <v>2.69</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O33" t="n">
-        <v>4.23</v>
+        <v>3.4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.6</v>
+        <v>3.02</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
         <v>2.9</v>
       </c>
       <c r="T33" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
         <v>1.4</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AA33" t="n">
         <v>3.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD33" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.12</v>
+        <v>1.31</v>
       </c>
       <c r="M35" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>8.74</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.69</v>
+        <v>3.75</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="O38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>8.74</v>
+        <v>2.9</v>
       </c>
       <c r="O40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5991,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6249,10 +6249,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6507,10 +6507,10 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6636,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6906,10 +6906,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.76</v>
+        <v>1.69</v>
       </c>
       <c r="M52" t="n">
-        <v>3.79</v>
+        <v>4.2</v>
       </c>
       <c r="N52" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,16 +7158,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="M53" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="N53" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,16 +7287,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="M54" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>7.9</v>
+        <v>4.7</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.64</v>
+        <v>3.76</v>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="N56" t="n">
-        <v>4.7</v>
+        <v>1.85</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="N5" t="n">
-        <v>4.32</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,65 +2729,65 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,17 +2987,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3903,34 +3903,34 @@
         <v>6.8</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y27" t="n">
         <v>1.8</v>
@@ -3939,16 +3939,16 @@
         <v>1.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4032,34 +4032,34 @@
         <v>3.57</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y28" t="n">
         <v>1.67</v>
@@ -4074,10 +4074,10 @@
         <v>1.55</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4277,65 +4277,65 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.79</v>
+        <v>2.69</v>
       </c>
       <c r="M30" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>4.25</v>
+        <v>2.25</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.8</v>
+        <v>3.02</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
         <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X30" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.59</v>
+        <v>2.33</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
-        <v>4.23</v>
+        <v>2.9</v>
       </c>
       <c r="P32" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="T32" t="n">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="U32" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="X32" t="n">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AB32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.69</v>
+        <v>2.12</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.82</v>
+        <v>2.23</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>8.74</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>8.74</v>
+        <v>2.9</v>
       </c>
       <c r="O35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.33</v>
+        <v>3.75</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="O36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5180,65 +5180,65 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>1.75</v>
+        <v>3.7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.8</v>
+        <v>3.59</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M40" t="n">
         <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5862,10 +5862,10 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5991,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -6096,28 +6096,28 @@
         <v>3.05</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W44" t="n">
         <v>1.65</v>
@@ -6126,22 +6126,22 @@
         <v>2.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="M46" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N46" t="n">
         <v>3.9</v>
       </c>
-      <c r="N46" t="n">
-        <v>7.5</v>
-      </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.33</v>
+        <v>2.92</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.15</v>
+        <v>1.42</v>
       </c>
       <c r="M48" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="N48" t="n">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6636,16 +6636,16 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>9.609999999999999</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>10.08</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.69</v>
+        <v>3.76</v>
       </c>
       <c r="M52" t="n">
-        <v>4.2</v>
+        <v>3.79</v>
       </c>
       <c r="N52" t="n">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7257,34 +7257,34 @@
         <v>7.9</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Y53" t="n">
         <v>1.63</v>
@@ -7299,10 +7299,10 @@
         <v>1.57</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N54" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.76</v>
+        <v>1.64</v>
       </c>
       <c r="M56" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK61"/>
+  <dimension ref="A1:AK54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,65 +2729,65 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,65 +2987,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.14</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>13</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" t="n">
         <v>1.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.54166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.5625</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.5625</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45917.5625</v>
+        <v>45917.57291666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45917.5625</v>
+        <v>45917.57291666666</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="O27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45917.57291666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>3.57</v>
+        <v>1.75</v>
       </c>
       <c r="O28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45917.57291666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.69</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.33</v>
+        <v>1.52</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.31</v>
+        <v>2.88</v>
       </c>
       <c r="M34" t="n">
-        <v>5.5</v>
+        <v>2.58</v>
       </c>
       <c r="N34" t="n">
-        <v>8.74</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.14</v>
+        <v>1.55</v>
       </c>
       <c r="X34" t="n">
-        <v>5.78</v>
+        <v>2.3</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N35" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5180,65 +5180,65 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="M37" t="n">
-        <v>3.64</v>
+        <v>2.8</v>
       </c>
       <c r="N37" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="O37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC37" t="n">
         <v>2.38</v>
       </c>
-      <c r="P37" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD37" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N38" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,19 +5509,19 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="N40" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,49 +5700,49 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N41" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
         <v>2.3</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5862,10 +5862,10 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.6</v>
+        <v>1.23</v>
       </c>
       <c r="M44" t="n">
+        <v>6</v>
+      </c>
+      <c r="N44" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X44" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z44" t="n">
         <v>2.7</v>
       </c>
-      <c r="N44" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O44" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T44" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AA44" t="n">
-        <v>7.8</v>
+        <v>2.07</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.07</v>
+        <v>1.72</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.4</v>
+        <v>4.05</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S45" t="n">
         <v>3.3</v>
       </c>
-      <c r="M45" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N45" t="n">
+      <c r="T45" t="n">
         <v>2.3</v>
       </c>
-      <c r="O45" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T45" t="n">
-        <v>4.05</v>
-      </c>
       <c r="U45" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="V45" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="W45" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="X45" t="n">
-        <v>2.45</v>
+        <v>4.55</v>
       </c>
       <c r="Y45" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>6.05</v>
+        <v>2.54</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.31</v>
+        <v>2.2</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="M46" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="N46" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O46" t="n">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="P46" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R46" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>2.18</v>
+        <v>3.6</v>
       </c>
       <c r="T46" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="U46" t="n">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="V46" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="W46" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X46" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB46" t="n">
         <v>1.6</v>
       </c>
-      <c r="X46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC46" t="n">
-        <v>2.38</v>
+        <v>1.55</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,27 +6820,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="M50" t="n">
-        <v>6</v>
+        <v>3.51</v>
       </c>
       <c r="N50" t="n">
-        <v>10.08</v>
+        <v>5.1</v>
       </c>
       <c r="O50" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.8125</v>
       </c>
     </row>
     <row r="51">
@@ -6949,27 +6949,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45917.64583333334</v>
+        <v>45917.85416666666</v>
       </c>
     </row>
     <row r="52">
@@ -7078,27 +7078,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.875</v>
       </c>
     </row>
     <row r="53">
@@ -7207,27 +7207,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="M53" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="N53" t="n">
-        <v>7.9</v>
+        <v>3.4</v>
       </c>
       <c r="O53" t="n">
-        <v>1.78</v>
+        <v>3.22</v>
       </c>
       <c r="P53" t="n">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>3.88</v>
       </c>
       <c r="R53" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U53" t="n">
         <v>1.25</v>
       </c>
-      <c r="S53" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.58</v>
-      </c>
       <c r="V53" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W53" t="n">
-        <v>1.13</v>
+        <v>2.45</v>
       </c>
       <c r="X53" t="n">
-        <v>5.6</v>
+        <v>1.55</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.4</v>
+        <v>4.63</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="AH53" t="n">
-        <v>3.1</v>
+        <v>1.53</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.89583333334</v>
       </c>
     </row>
     <row r="54">
@@ -7336,27 +7336,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.69</v>
+        <v>2.85</v>
       </c>
       <c r="M54" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="N54" t="n">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="O54" t="n">
-        <v>2.23</v>
+        <v>3.25</v>
       </c>
       <c r="P54" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="R54" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S54" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T54" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="U54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X54" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC54" t="n">
         <v>1.62</v>
       </c>
-      <c r="V54" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X54" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AD54" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7456,909 +7456,6 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45917.66666666666</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Morocco Botola Pro</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Raja Casablanca</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>FAR Rabat</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" s="3" t="n">
-        <v>45917.66666666666</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Atlético Madrid</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M56" t="n">
-        <v>4</v>
-      </c>
-      <c r="N56" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O56" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P56" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X56" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" s="3" t="n">
-        <v>45917.66666666666</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Botafogo</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Mirassol</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="N57" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK57" s="3" t="n">
-        <v>45917.8125</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Columbus Crew</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="M58" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O58" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P58" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>3</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S58" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T58" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X58" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK58" s="3" t="n">
-        <v>45917.85416666666</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Houston Dynamo FC II</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK59" s="3" t="n">
-        <v>45917.875</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>River Plate</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N60" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="X60" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK60" s="3" t="n">
-        <v>45917.89583333334</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M61" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N61" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O61" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P61" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S61" t="n">
-        <v>3</v>
-      </c>
-      <c r="T61" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X61" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG61" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK61" s="3" t="n">
         <v>45917.9375</v>
       </c>
     </row>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK54"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45917.46875</v>
+        <v>45917.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45917.47916666666</v>
+        <v>45917.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45917.47916666666</v>
+        <v>45917.46875</v>
       </c>
     </row>
     <row r="9">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45917.48958333334</v>
+        <v>45917.47916666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.48958333334</v>
       </c>
     </row>
     <row r="17">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.5</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.5</v>
       </c>
     </row>
     <row r="22">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45917.5625</v>
+        <v>45917.54166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45917.5625</v>
+        <v>45917.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45917.57291666666</v>
+        <v>45917.5625</v>
       </c>
     </row>
     <row r="26">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.57</v>
+        <v>3.05</v>
       </c>
       <c r="O26" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>2.61</v>
       </c>
       <c r="U26" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
-        <v>4.6</v>
+        <v>3.68</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45917.57291666666</v>
+        <v>45917.5625</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.9</v>
+        <v>3.57</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.57291666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,62 +4023,62 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.75</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.75</v>
       </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.57291666666</v>
       </c>
     </row>
     <row r="29">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
-        <v>3.7</v>
+        <v>1.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.52</v>
+        <v>2.35</v>
       </c>
       <c r="M32" t="n">
-        <v>3.41</v>
+        <v>3.65</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4806,28 +4806,28 @@
         <v>2.6</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W34" t="n">
         <v>1.55</v>
@@ -4836,22 +4836,22 @@
         <v>2.3</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M37" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="O37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5325,13 +5325,13 @@
         <v>4.22</v>
       </c>
       <c r="P38" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="R38" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="S38" t="n">
         <v>2.18</v>
@@ -5343,7 +5343,7 @@
         <v>1.18</v>
       </c>
       <c r="V38" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="W38" t="n">
         <v>1.48</v>
@@ -5352,10 +5352,10 @@
         <v>2.45</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AA38" t="n">
         <v>6.05</v>
@@ -5364,10 +5364,10 @@
         <v>1.06</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.42</v>
+        <v>2.15</v>
       </c>
       <c r="M41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N41" t="n">
         <v>3.9</v>
       </c>
-      <c r="N41" t="n">
-        <v>8.5</v>
-      </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -6087,19 +6087,19 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M44" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="N44" t="n">
-        <v>10.08</v>
+        <v>12</v>
       </c>
       <c r="O44" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="P44" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="Q44" t="n">
         <v>7.5</v>
@@ -6111,7 +6111,7 @@
         <v>3.85</v>
       </c>
       <c r="T44" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="U44" t="n">
         <v>1.71</v>
@@ -6120,10 +6120,10 @@
         <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X44" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="Y44" t="n">
         <v>1.38</v>
@@ -6135,7 +6135,7 @@
         <v>2.07</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC44" t="n">
         <v>1.83</v>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AH44" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.64583333334</v>
       </c>
     </row>
     <row r="46">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="M46" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="N46" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="O46" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="P46" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="R46" t="n">
         <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="T46" t="n">
         <v>2.2</v>
       </c>
       <c r="U46" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V46" t="n">
         <v>1.02</v>
       </c>
       <c r="W46" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,77 +6474,77 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.76</v>
+        <v>1.69</v>
       </c>
       <c r="M47" t="n">
-        <v>3.79</v>
+        <v>4.2</v>
       </c>
       <c r="N47" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>2.23</v>
       </c>
       <c r="P47" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="R47" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T47" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U47" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="V47" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W47" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X47" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
         <v>1.22</v>
       </c>
-      <c r="X47" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH47" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="M49" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>7.9</v>
+        <v>4.7</v>
       </c>
       <c r="O49" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="P49" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="R49" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S49" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="T49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X49" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z49" t="n">
         <v>2.2</v>
       </c>
-      <c r="U49" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X49" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AA49" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AH49" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6820,27 +6820,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45917.8125</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="M51" t="n">
-        <v>3.66</v>
+        <v>3.51</v>
       </c>
       <c r="N51" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="O51" t="n">
-        <v>2.84</v>
+        <v>2.23</v>
       </c>
       <c r="P51" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="R51" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="S51" t="n">
-        <v>3.35</v>
+        <v>2.57</v>
       </c>
       <c r="T51" t="n">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="U51" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="V51" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W51" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="X51" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45917.85416666666</v>
+        <v>45917.8125</v>
       </c>
     </row>
     <row r="52">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45917.875</v>
+        <v>45917.85416666666</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45917.89583333334</v>
+        <v>45917.875</v>
       </c>
     </row>
     <row r="54">
@@ -7336,126 +7336,255 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W54" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="3" t="n">
+        <v>45917.89583333334</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Real Salt Lake</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L54" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="M54" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O54" t="n">
+      <c r="L55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O55" t="n">
         <v>3.25</v>
       </c>
-      <c r="P54" t="n">
+      <c r="P55" t="n">
         <v>2.26</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q55" t="n">
         <v>3</v>
       </c>
-      <c r="R54" t="n">
+      <c r="R55" t="n">
         <v>1.33</v>
       </c>
-      <c r="S54" t="n">
+      <c r="S55" t="n">
         <v>3</v>
       </c>
-      <c r="T54" t="n">
+      <c r="T55" t="n">
         <v>2.53</v>
       </c>
-      <c r="U54" t="n">
+      <c r="U55" t="n">
         <v>1.5</v>
       </c>
-      <c r="V54" t="n">
+      <c r="V55" t="n">
         <v>1.05</v>
       </c>
-      <c r="W54" t="n">
+      <c r="W55" t="n">
         <v>1.21</v>
       </c>
-      <c r="X54" t="n">
+      <c r="X55" t="n">
         <v>4.21</v>
       </c>
-      <c r="Y54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA54" t="n">
+      <c r="Y55" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA55" t="n">
         <v>2.71</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AB55" t="n">
         <v>1.44</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AC55" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AD55" t="n">
         <v>2.34</v>
       </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
         <v>1.29</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AH55" t="n">
         <v>1.45</v>
       </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" s="3" t="n">
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="3" t="n">
         <v>45917.9375</v>
       </c>
     </row>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45917.46875</v>
+        <v>45917.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45917.47916666666</v>
+        <v>45917.46875</v>
       </c>
     </row>
     <row r="10">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45917.48958333334</v>
+        <v>45917.47916666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.48958333334</v>
       </c>
     </row>
     <row r="18">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="M18" t="n">
         <v>3.41</v>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
         <v>3.7</v>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.52083333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.54166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,43 +3378,43 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="M23" t="n">
         <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="P23" t="n">
         <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="Y23" t="n">
         <v>1.8</v>
@@ -3423,16 +3423,16 @@
         <v>1.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.5625</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.5625</v>
       </c>
     </row>
     <row r="25">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.17</v>
+        <v>1.43</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.05</v>
+        <v>6.8</v>
       </c>
       <c r="O26" t="n">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.62</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="T26" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="Y26" t="n">
         <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
         <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45917.5625</v>
+        <v>45917.57291666666</v>
       </c>
     </row>
     <row r="27">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AA28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45917.57291666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.75</v>
       </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.12</v>
+        <v>3.75</v>
       </c>
       <c r="M31" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="O34" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
         <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="N37" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.6</v>
+        <v>1.42</v>
       </c>
       <c r="M39" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>3.05</v>
+        <v>8.5</v>
       </c>
       <c r="O39" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.34</v>
+        <v>2.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AA39" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="M44" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="N44" t="n">
         <v>12</v>
       </c>
       <c r="O44" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P44" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R44" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S44" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="T44" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V44" t="n">
         <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X44" t="n">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.65</v>
+        <v>4.08</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="N47" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="O47" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="P47" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="R47" t="n">
         <v>1.25</v>
       </c>
       <c r="S47" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="T47" t="n">
         <v>2.2</v>
       </c>
       <c r="U47" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V47" t="n">
         <v>1.02</v>
       </c>
       <c r="W47" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X47" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,77 +6603,77 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.76</v>
+        <v>1.69</v>
       </c>
       <c r="M48" t="n">
-        <v>3.79</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>2.23</v>
       </c>
       <c r="P48" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="R48" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T48" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U48" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="V48" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W48" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X48" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
         <v>1.22</v>
       </c>
-      <c r="X48" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH48" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -7119,28 +7119,28 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="M52" t="n">
-        <v>3.29</v>
+        <v>3.66</v>
       </c>
       <c r="N52" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="O52" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="P52" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q52" t="n">
         <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S52" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="T52" t="n">
         <v>2.25</v>
@@ -7155,19 +7155,19 @@
         <v>1.24</v>
       </c>
       <c r="X52" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AC52" t="n">
         <v>1.57</v>
@@ -7189,7 +7189,7 @@
         <v>1.4</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="M55" t="n">
-        <v>3.31</v>
+        <v>3.58</v>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="O55" t="n">
         <v>3.25</v>
       </c>
       <c r="P55" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="R55" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T55" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U55" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V55" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W55" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X55" t="n">
-        <v>4.21</v>
+        <v>4</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>1.29</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>2.19</v>
       </c>
       <c r="M8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA8" t="n">
         <v>5.5</v>
       </c>
-      <c r="N8" t="n">
-        <v>16</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.79</v>
+        <v>2.21</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.3</v>
+        <v>1.56</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2739,7 +2739,7 @@
         <v>3.41</v>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="O18" t="n">
         <v>3.7</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3252,52 +3252,52 @@
         <v>2.32</v>
       </c>
       <c r="M22" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
         <v>2.74</v>
       </c>
       <c r="O22" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="P22" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="T22" t="n">
         <v>2.59</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AA22" t="n">
         <v>2.98</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AC22" t="n">
         <v>1.65</v>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
         <v>1.56</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="P29" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH29" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.52</v>
+        <v>3.75</v>
       </c>
       <c r="M30" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>1.75</v>
       </c>
       <c r="O30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.79</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4929,58 +4929,58 @@
         <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
         <v>3.2</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="N36" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="M37" t="n">
-        <v>2.58</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="O37" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.67</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.46</v>
+        <v>2.23</v>
       </c>
       <c r="AA37" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.3</v>
+        <v>8.5</v>
       </c>
       <c r="M38" t="n">
-        <v>2.85</v>
+        <v>4.33</v>
       </c>
       <c r="N38" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="O38" t="n">
-        <v>4.22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P38" t="n">
-        <v>1.82</v>
+        <v>2.26</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.48</v>
+        <v>1.85</v>
       </c>
       <c r="R38" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="T38" t="n">
-        <v>4.05</v>
+        <v>2.84</v>
       </c>
       <c r="U38" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="V38" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="X38" t="n">
-        <v>2.45</v>
+        <v>3.22</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AA38" t="n">
-        <v>6.05</v>
+        <v>3.34</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.31</v>
+        <v>1.03</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N39" t="n">
         <v>3.9</v>
       </c>
-      <c r="N39" t="n">
-        <v>8.5</v>
-      </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O41" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X41" t="n">
         <v>2.15</v>
       </c>
-      <c r="M41" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA41" t="n">
         <v>6.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="M43" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="n">
-        <v>3.05</v>
+        <v>6.5</v>
       </c>
       <c r="O43" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>3.34</v>
+        <v>2.3</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AA43" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6090,58 +6090,58 @@
         <v>1.2</v>
       </c>
       <c r="M44" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="N44" t="n">
         <v>12</v>
       </c>
       <c r="O44" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="P44" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="Q44" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="R44" t="n">
         <v>1.2</v>
       </c>
       <c r="S44" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="U44" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="V44" t="n">
         <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X44" t="n">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AA44" t="n">
         <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AH44" t="n">
-        <v>4.08</v>
+        <v>3.7</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,77 +6603,77 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.69</v>
+        <v>3.76</v>
       </c>
       <c r="M48" t="n">
-        <v>4.2</v>
+        <v>3.79</v>
       </c>
       <c r="N48" t="n">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="O48" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q48" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q48" t="n">
-        <v>4.33</v>
-      </c>
       <c r="R48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH48" t="n">
         <v>1.25</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X48" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>2.1</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,77 +6732,77 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O49" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X49" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH49" t="n">
         <v>2.1</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X49" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>2.2</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6999,19 +6999,19 @@
         <v>5.1</v>
       </c>
       <c r="O51" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="P51" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="R51" t="n">
         <v>1.42</v>
       </c>
       <c r="S51" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="T51" t="n">
         <v>3.04</v>
@@ -7023,29 +7023,29 @@
         <v>1.02</v>
       </c>
       <c r="W51" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X51" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="Y51" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC51" t="n">
         <v>2.15</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AD51" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA51" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AE51" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7119,16 +7119,16 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="M52" t="n">
-        <v>3.66</v>
+        <v>3.29</v>
       </c>
       <c r="N52" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="O52" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="P52" t="n">
         <v>2.38</v>
@@ -7155,19 +7155,19 @@
         <v>1.24</v>
       </c>
       <c r="X52" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC52" t="n">
         <v>1.57</v>
@@ -7189,7 +7189,7 @@
         <v>1.4</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7506,25 +7506,25 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="M55" t="n">
-        <v>3.58</v>
+        <v>3.31</v>
       </c>
       <c r="N55" t="n">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="O55" t="n">
         <v>3.25</v>
       </c>
       <c r="P55" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="Q55" t="n">
         <v>3.15</v>
       </c>
       <c r="R55" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S55" t="n">
         <v>3.1</v>
@@ -7536,31 +7536,31 @@
         <v>1.53</v>
       </c>
       <c r="V55" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W55" t="n">
         <v>1.2</v>
       </c>
       <c r="X55" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.31</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>2.56</v>
+        <v>5.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.88</v>
+        <v>16</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>6.8</v>
+        <v>3.57</v>
       </c>
       <c r="O26" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="P26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q26" t="n">
-        <v>7</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.62</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.57</v>
+        <v>6.8</v>
       </c>
       <c r="O27" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>3.62</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.88</v>
+        <v>2.75</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
-        <v>2.34</v>
+        <v>3.15</v>
       </c>
       <c r="P28" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.03</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>4.76</v>
+        <v>3.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.39</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.36</v>
+        <v>2.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>2.8</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>2.75</v>
       </c>
       <c r="O29" t="n">
-        <v>2.16</v>
+        <v>3.44</v>
       </c>
       <c r="P29" t="n">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.69</v>
+        <v>3.55</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="S29" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="U29" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Z29" t="n">
         <v>1.41</v>
       </c>
-      <c r="X29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AA29" t="n">
-        <v>4.19</v>
+        <v>5.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="P31" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>3.77</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4569,7 +4569,7 @@
         <v>1.47</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
         <v>1.22</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="M36" t="n">
-        <v>2.8</v>
+        <v>3.98</v>
       </c>
       <c r="N36" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="O36" t="n">
-        <v>3.44</v>
+        <v>2.34</v>
       </c>
       <c r="P36" t="n">
-        <v>1.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.55</v>
+        <v>4.03</v>
       </c>
       <c r="R36" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="S36" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA36" t="n">
         <v>2.36</v>
       </c>
-      <c r="T36" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W36" t="n">
+      <c r="AB36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC36" t="n">
         <v>1.5</v>
       </c>
-      <c r="X36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AD36" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="M37" t="n">
         <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="M38" t="n">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="N38" t="n">
-        <v>1.36</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
-        <v>8.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="P38" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="S38" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="T38" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W38" t="n">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="X38" t="n">
-        <v>3.22</v>
+        <v>2.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.95</v>
+        <v>3.34</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.34</v>
+        <v>7.7</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="M39" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
       <c r="O39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AA39" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="M42" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="N42" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="O42" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P42" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="R42" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="S42" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="T42" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="U42" t="n">
         <v>1.18</v>
       </c>
       <c r="V42" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="W42" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="X42" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="Y42" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AA42" t="n">
-        <v>7.7</v>
+        <v>6.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.48</v>
       </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.44</v>
+        <v>8.5</v>
       </c>
       <c r="M43" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>6.5</v>
+        <v>1.37</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="O46" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="P46" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="R46" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="T46" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U46" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="V46" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W46" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X46" t="n">
-        <v>4.55</v>
+        <v>5.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,62 +6474,62 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="M47" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="N47" t="n">
-        <v>7.9</v>
+        <v>4.2</v>
       </c>
       <c r="O47" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="P47" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="R47" t="n">
         <v>1.25</v>
       </c>
       <c r="S47" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="T47" t="n">
         <v>2.2</v>
       </c>
       <c r="U47" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V47" t="n">
         <v>1.02</v>
       </c>
       <c r="W47" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X47" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AA47" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD47" t="n">
         <v>2.4</v>
       </c>
-      <c r="AB47" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE47" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.76</v>
+        <v>1.64</v>
       </c>
       <c r="M48" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="P48" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="R48" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T48" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U48" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="V48" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W48" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X48" t="n">
-        <v>3.92</v>
+        <v>4.55</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AC48" t="n">
         <v>1.65</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,77 +6732,77 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.69</v>
+        <v>3.76</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>3.79</v>
       </c>
       <c r="N49" t="n">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="O49" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q49" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q49" t="n">
-        <v>4.33</v>
-      </c>
       <c r="R49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH49" t="n">
         <v>1.25</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X49" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>2.1</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>1.96</v>
       </c>
       <c r="M6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA6" t="n">
         <v>5.5</v>
       </c>
-      <c r="N6" t="n">
-        <v>16</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.04</v>
+        <v>2.21</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.2</v>
+        <v>1.56</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.91</v>
+        <v>4.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
         <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="O21" t="n">
         <v>2.9</v>
@@ -3141,13 +3141,13 @@
         <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="T21" t="n">
         <v>2.59</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
@@ -3159,10 +3159,10 @@
         <v>3.44</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AA21" t="n">
         <v>2.98</v>
@@ -3190,7 +3190,7 @@
         <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="O28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="M29" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA29" t="n">
         <v>2.75</v>
       </c>
-      <c r="O29" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U29" t="n">
+      <c r="AB29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.22</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="P30" t="n">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="S30" t="n">
-        <v>3.04</v>
+        <v>2.23</v>
       </c>
       <c r="T30" t="n">
-        <v>2.48</v>
+        <v>3.65</v>
       </c>
       <c r="U30" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="X30" t="n">
-        <v>3.95</v>
+        <v>2.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.74</v>
+        <v>2.52</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.09</v>
+        <v>1.41</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.39</v>
+        <v>1.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
         <v>3.2</v>
       </c>
       <c r="O31" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="P31" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.77</v>
+        <v>4.09</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="T31" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="U31" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X31" t="n">
-        <v>4.6</v>
+        <v>3.84</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z31" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AD31" t="n">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AH31" t="n">
         <v>1.75</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>3.93</v>
+        <v>2.6</v>
       </c>
       <c r="O32" t="n">
-        <v>2.31</v>
+        <v>3.15</v>
       </c>
       <c r="P32" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.49</v>
+        <v>3.15</v>
       </c>
       <c r="R32" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.97</v>
+        <v>1.45</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O33" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.09</v>
+        <v>4.03</v>
       </c>
       <c r="R33" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="S33" t="n">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="T33" t="n">
-        <v>2.58</v>
+        <v>2.27</v>
       </c>
       <c r="U33" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>3.84</v>
+        <v>4.76</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.95</v>
+        <v>2.36</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="P34" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.69</v>
+        <v>3.77</v>
       </c>
       <c r="R34" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="V34" t="n">
         <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="X34" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.22</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.59</v>
+        <v>2.23</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.19</v>
+        <v>2.65</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.19</v>
+        <v>1.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.57</v>
+        <v>2.39</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="M36" t="n">
-        <v>3.98</v>
+        <v>3.41</v>
       </c>
       <c r="N36" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="P36" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.03</v>
+        <v>5.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="S36" t="n">
-        <v>3.48</v>
+        <v>2.55</v>
       </c>
       <c r="T36" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.16</v>
       </c>
-      <c r="X36" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AC36" t="n">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.34</v>
+        <v>1.6</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.6</v>
+        <v>1.42</v>
       </c>
       <c r="M38" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>8.5</v>
       </c>
       <c r="O38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.34</v>
+        <v>2.3</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.42</v>
+        <v>8.5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N39" t="n">
-        <v>8.5</v>
+        <v>1.37</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>8.5</v>
+        <v>2.15</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="N43" t="n">
-        <v>1.37</v>
+        <v>3.9</v>
       </c>
       <c r="O43" t="n">
-        <v>8.25</v>
+        <v>2.72</v>
       </c>
       <c r="P43" t="n">
-        <v>2.13</v>
+        <v>1.74</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.94</v>
+        <v>6.14</v>
       </c>
       <c r="R43" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="S43" t="n">
-        <v>2.56</v>
+        <v>2.09</v>
       </c>
       <c r="T43" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="U43" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W43" t="n">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="X43" t="n">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.88</v>
+        <v>3</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.82</v>
+        <v>1.36</v>
       </c>
       <c r="AA43" t="n">
-        <v>4</v>
+        <v>6.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.03</v>
+        <v>1.77</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,77 +6345,77 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.33</v>
+        <v>3.76</v>
       </c>
       <c r="M46" t="n">
-        <v>5.2</v>
+        <v>3.79</v>
       </c>
       <c r="N46" t="n">
-        <v>7.9</v>
+        <v>1.85</v>
       </c>
       <c r="O46" t="n">
-        <v>1.78</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="R46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X46" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH46" t="n">
         <v>1.25</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X46" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>3.1</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O47" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="P47" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="R47" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S47" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X47" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z47" t="n">
         <v>2.2</v>
       </c>
-      <c r="U47" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X47" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AA47" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,77 +6603,77 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O48" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X48" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH48" t="n">
         <v>2.1</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X48" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>2.2</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6990,34 +6990,34 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M51" t="n">
-        <v>3.51</v>
+        <v>3.75</v>
       </c>
       <c r="N51" t="n">
-        <v>5.1</v>
+        <v>5.43</v>
       </c>
       <c r="O51" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="P51" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q51" t="n">
         <v>6.2</v>
       </c>
       <c r="R51" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S51" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T51" t="n">
         <v>3.04</v>
       </c>
       <c r="U51" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="V51" t="n">
         <v>1.02</v>
@@ -7029,16 +7029,16 @@
         <v>3.15</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC51" t="n">
         <v>2.15</v>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>16</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="X7" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.17</v>
+        <v>4.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.56</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.77</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,16 +2250,16 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.75</v>
+        <v>1.52</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.88</v>
+        <v>1.79</v>
       </c>
       <c r="M30" t="n">
-        <v>2.58</v>
+        <v>3.98</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S30" t="n">
         <v>3.48</v>
       </c>
-      <c r="P30" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.23</v>
-      </c>
       <c r="T30" t="n">
-        <v>3.65</v>
+        <v>2.27</v>
       </c>
       <c r="U30" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.55</v>
       </c>
-      <c r="X30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AC30" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>2.49</v>
+        <v>3.15</v>
       </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.09</v>
+        <v>3.15</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U31" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AA31" t="n">
         <v>2.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.3</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="U32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z32" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA32" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,77 +4668,77 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O33" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="P33" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.03</v>
+        <v>4.09</v>
       </c>
       <c r="R33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.24</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X33" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z34" t="n">
         <v>2.1</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AA34" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.52</v>
+        <v>3.75</v>
       </c>
       <c r="M36" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>1.75</v>
       </c>
       <c r="O36" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="N37" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="P37" t="n">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R37" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="S37" t="n">
-        <v>3.04</v>
+        <v>2.23</v>
       </c>
       <c r="T37" t="n">
-        <v>2.48</v>
+        <v>3.65</v>
       </c>
       <c r="U37" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W37" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="X37" t="n">
-        <v>3.95</v>
+        <v>2.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.74</v>
+        <v>2.52</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.09</v>
+        <v>1.41</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.39</v>
+        <v>1.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.42</v>
+        <v>3.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="N38" t="n">
-        <v>8.5</v>
+        <v>2.3</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>8.5</v>
+        <v>2.15</v>
       </c>
       <c r="M39" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="N39" t="n">
-        <v>1.37</v>
+        <v>3.9</v>
       </c>
       <c r="O39" t="n">
-        <v>8.25</v>
+        <v>2.72</v>
       </c>
       <c r="P39" t="n">
-        <v>2.13</v>
+        <v>1.74</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.94</v>
+        <v>6.14</v>
       </c>
       <c r="R39" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="S39" t="n">
-        <v>2.56</v>
+        <v>2.09</v>
       </c>
       <c r="T39" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="U39" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W39" t="n">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="X39" t="n">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.88</v>
+        <v>3</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.82</v>
+        <v>1.36</v>
       </c>
       <c r="AA39" t="n">
-        <v>4</v>
+        <v>6.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.03</v>
+        <v>1.77</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.15</v>
+        <v>1.42</v>
       </c>
       <c r="M43" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="n">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
       <c r="O43" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="M51" t="n">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="N51" t="n">
-        <v>5.43</v>
+        <v>5.1</v>
       </c>
       <c r="O51" t="n">
         <v>2.21</v>
@@ -7029,10 +7029,10 @@
         <v>3.15</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA51" t="n">
         <v>3.82</v>
@@ -7119,19 +7119,19 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="M52" t="n">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
       <c r="N52" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="O52" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P52" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q52" t="n">
         <v>3</v>
@@ -7158,16 +7158,16 @@
         <v>3.8</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AC52" t="n">
         <v>1.57</v>
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="M55" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="O55" t="n">
         <v>3.25</v>
@@ -7521,7 +7521,7 @@
         <v>2.22</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R55" t="n">
         <v>1.3</v>
@@ -7542,22 +7542,22 @@
         <v>1.2</v>
       </c>
       <c r="X55" t="n">
-        <v>3.98</v>
+        <v>4.46</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AD55" t="n">
         <v>2.25</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK55"/>
+  <dimension ref="A1:AK60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.2</v>
+        <v>1.96</v>
       </c>
       <c r="M5" t="n">
-        <v>5.5</v>
+        <v>2.77</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6</v>
+        <v>3.15</v>
       </c>
       <c r="P5" t="n">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.75</v>
+        <v>3.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="U5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.41</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AA5" t="n">
-        <v>2.95</v>
+        <v>5.64</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.2</v>
+        <v>1.59</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1323,28 +1323,28 @@
         <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
         <v>1.75</v>
@@ -1353,22 +1353,22 @@
         <v>1.95</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>7.29</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>2.77</v>
+        <v>5.5</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O8" t="n">
-        <v>3.02</v>
+        <v>1.62</v>
       </c>
       <c r="P8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AA8" t="n">
-        <v>5.5</v>
+        <v>2.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.21</v>
+        <v>3.04</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.56</v>
+        <v>4.45</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1581,34 +1581,34 @@
         <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
         <v>1.53</v>
@@ -1617,16 +1617,16 @@
         <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>1.77</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>2.86</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.6</v>
+        <v>2.99</v>
       </c>
       <c r="M18" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="O18" t="n">
         <v>3.7</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.52</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
+        <v>2.55</v>
       </c>
       <c r="O28" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>2.82</v>
+        <v>3.37</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.18</v>
+        <v>1.48</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>2.58</v>
       </c>
       <c r="N29" t="n">
-        <v>3.93</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.31</v>
+        <v>3.25</v>
       </c>
       <c r="P29" t="n">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.49</v>
+        <v>3.55</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="S29" t="n">
-        <v>3.14</v>
+        <v>2.23</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>3.65</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="X29" t="n">
-        <v>3.95</v>
+        <v>2.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.71</v>
+        <v>2.52</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.06</v>
+        <v>1.41</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.75</v>
+        <v>5.18</v>
       </c>
       <c r="AB29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.41</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.97</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,77 +4281,77 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="P30" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.03</v>
+        <v>3.65</v>
       </c>
       <c r="R30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
         <v>1.24</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X30" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="O31" t="n">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="P31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z31" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA31" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>2.59</v>
       </c>
       <c r="O32" t="n">
-        <v>2.43</v>
+        <v>2.72</v>
       </c>
       <c r="P32" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.77</v>
+        <v>2.95</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="T32" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="U32" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>4.44</v>
+        <v>3.92</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.36</v>
+        <v>1.31</v>
       </c>
       <c r="M34" t="n">
-        <v>3.23</v>
+        <v>5.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.59</v>
+        <v>8.74</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="P34" t="n">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.33</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>3.04</v>
+        <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>2.42</v>
+        <v>1.98</v>
       </c>
       <c r="U34" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="V34" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>4.08</v>
+        <v>5.78</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.75</v>
+        <v>1.98</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.47</v>
+        <v>3.4</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,62 +5184,62 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.88</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="O37" t="n">
-        <v>3.48</v>
+        <v>2.23</v>
       </c>
       <c r="P37" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>2.23</v>
+        <v>3.04</v>
       </c>
       <c r="T37" t="n">
-        <v>3.65</v>
+        <v>2.52</v>
       </c>
       <c r="U37" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="V37" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="X37" t="n">
-        <v>2.3</v>
+        <v>3.84</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.52</v>
+        <v>1.7</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.41</v>
+        <v>2.04</v>
       </c>
       <c r="AA37" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="AC37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD37" t="n">
         <v>2.07</v>
       </c>
-      <c r="AD37" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.3</v>
+        <v>1.52</v>
       </c>
       <c r="M38" t="n">
-        <v>2.85</v>
+        <v>3.41</v>
       </c>
       <c r="N38" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
-        <v>4.05</v>
+        <v>2.16</v>
       </c>
       <c r="P38" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.48</v>
+        <v>6.3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="S38" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="T38" t="n">
-        <v>4.05</v>
+        <v>3.28</v>
       </c>
       <c r="U38" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="V38" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="X38" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.31</v>
+        <v>2.26</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M39" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="O39" t="n">
-        <v>2.72</v>
+        <v>2.38</v>
       </c>
       <c r="P39" t="n">
-        <v>1.74</v>
+        <v>2.32</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.14</v>
+        <v>3.56</v>
       </c>
       <c r="R39" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="S39" t="n">
-        <v>2.09</v>
+        <v>3.42</v>
       </c>
       <c r="T39" t="n">
-        <v>4.15</v>
+        <v>2.27</v>
       </c>
       <c r="U39" t="n">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="V39" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="X39" t="n">
-        <v>2.2</v>
+        <v>4.81</v>
       </c>
       <c r="Y39" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.36</v>
+        <v>2.28</v>
       </c>
       <c r="AA39" t="n">
-        <v>6.15</v>
+        <v>2.42</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.38</v>
+        <v>1.48</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>8.5</v>
+        <v>3.75</v>
       </c>
       <c r="M40" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="O40" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O41" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q41" t="n">
         <v>2.6</v>
       </c>
-      <c r="M41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>3.9</v>
-      </c>
       <c r="R41" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="S41" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="T41" t="n">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="U41" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="V41" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="W41" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="X41" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="AA41" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,19 +5767,19 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="42">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.42</v>
+        <v>3.3</v>
       </c>
       <c r="M43" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="N43" t="n">
-        <v>8.5</v>
+        <v>2.3</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,62 +6216,62 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="M45" t="n">
-        <v>3.96</v>
+        <v>2.8</v>
       </c>
       <c r="N45" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O45" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X45" t="n">
         <v>2.2</v>
       </c>
-      <c r="P45" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X45" t="n">
-        <v>4.4</v>
-      </c>
       <c r="Y45" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.6</v>
+        <v>6.15</v>
       </c>
       <c r="AB45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.47</v>
       </c>
-      <c r="AC45" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.13</v>
-      </c>
       <c r="AE45" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.07</v>
+        <v>1.76</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45917.64583333334</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.76</v>
+        <v>1.42</v>
       </c>
       <c r="M46" t="n">
-        <v>3.79</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>1.85</v>
+        <v>8.5</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="M48" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="N48" t="n">
-        <v>4.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="P48" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.33</v>
+        <v>7.7</v>
       </c>
       <c r="R48" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S48" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T48" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="U48" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V48" t="n">
         <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X48" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.1</v>
+        <v>3.44</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="M50" t="n">
-        <v>5.2</v>
+        <v>3.69</v>
       </c>
       <c r="N50" t="n">
-        <v>7.9</v>
+        <v>3.98</v>
       </c>
       <c r="O50" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>4.55</v>
       </c>
       <c r="R50" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S50" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="T50" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="U50" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="V50" t="n">
         <v>1.02</v>
       </c>
       <c r="W50" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X50" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.64583333334</v>
       </c>
     </row>
     <row r="51">
@@ -6949,27 +6949,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="M51" t="n">
-        <v>3.51</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="O51" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="P51" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q51" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="R51" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S51" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="T51" t="n">
-        <v>3.04</v>
+        <v>2.3</v>
       </c>
       <c r="U51" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V51" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W51" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="X51" t="n">
-        <v>3.15</v>
+        <v>4.55</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.82</v>
+        <v>2.54</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45917.8125</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="52">
@@ -7078,27 +7078,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.33</v>
+        <v>3.76</v>
       </c>
       <c r="M52" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N52" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R52" t="n">
         <v>1.3</v>
       </c>
       <c r="S52" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U52" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="V52" t="n">
         <v>1.04</v>
       </c>
       <c r="W52" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X52" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45917.85416666666</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="53">
@@ -7207,27 +7207,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45917.875</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="54">
@@ -7336,27 +7336,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45917.89583333334</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="55">
@@ -7465,126 +7465,771 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Bayern München</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M55" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X55" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="3" t="n">
+        <v>45917.66666666666</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N56" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O56" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="3" t="n">
+        <v>45917.8125</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>3</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X57" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="3" t="n">
+        <v>45917.85416666666</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC II</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X58" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3" t="n">
+        <v>45917.875</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O59" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X59" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="3" t="n">
+        <v>45917.89583333334</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Real Salt Lake</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L55" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N55" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O55" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3</v>
-      </c>
-      <c r="R55" t="n">
+      <c r="L60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O60" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R60" t="n">
         <v>1.3</v>
       </c>
-      <c r="S55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T55" t="n">
+      <c r="S60" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T60" t="n">
         <v>2.5</v>
       </c>
-      <c r="U55" t="n">
+      <c r="U60" t="n">
         <v>1.53</v>
       </c>
-      <c r="V55" t="n">
+      <c r="V60" t="n">
         <v>1.03</v>
       </c>
-      <c r="W55" t="n">
+      <c r="W60" t="n">
         <v>1.2</v>
       </c>
-      <c r="X55" t="n">
+      <c r="X60" t="n">
         <v>4.46</v>
       </c>
-      <c r="Y55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA55" t="n">
+      <c r="Y60" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA60" t="n">
         <v>2.67</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AB60" t="n">
         <v>1.47</v>
       </c>
-      <c r="AC55" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" s="3" t="n">
+      <c r="AC60" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="3" t="n">
         <v>45917.9375</v>
       </c>
     </row>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK60"/>
+  <dimension ref="A1:AK54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1572,31 +1572,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S9" t="n">
         <v>3.34</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T9" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="U9" t="n">
         <v>1.57</v>
@@ -1608,25 +1608,25 @@
         <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45917.5</v>
+        <v>45917.52083333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45917.52083333334</v>
+        <v>45917.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.71</v>
+        <v>2.17</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.5625</v>
       </c>
     </row>
     <row r="23">
@@ -3381,58 +3381,58 @@
         <v>11</v>
       </c>
       <c r="M23" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="N23" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45917.5625</v>
+        <v>45917.57291666666</v>
       </c>
     </row>
     <row r="26">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,86 +3894,86 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="N27" t="n">
-        <v>6.8</v>
+        <v>8.74</v>
       </c>
       <c r="O27" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q27" t="n">
         <v>7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X27" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z27" t="n">
         <v>2.9</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X27" t="n">
+      <c r="AA27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH27" t="n">
         <v>3.4</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45917.57291666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="28">
@@ -4023,22 +4023,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N28" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="O28" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P28" t="n">
         <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="R28" t="n">
         <v>1.38</v>
@@ -4059,7 +4059,7 @@
         <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>3.37</v>
+        <v>3.14</v>
       </c>
       <c r="Y28" t="n">
         <v>1.91</v>
@@ -4068,7 +4068,7 @@
         <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.14</v>
+        <v>3.33</v>
       </c>
       <c r="AB28" t="n">
         <v>1.27</v>
@@ -4077,7 +4077,7 @@
         <v>1.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.88</v>
+        <v>1.71</v>
       </c>
       <c r="M29" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>3.25</v>
+        <v>2.28</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.55</v>
+        <v>4.83</v>
       </c>
       <c r="R29" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>2.23</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>3.65</v>
+        <v>2.49</v>
       </c>
       <c r="U29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.22</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.41</v>
+        <v>2.04</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>2.59</v>
       </c>
       <c r="O30" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="T30" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X30" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
         <v>2.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P31" t="n">
         <v>1.95</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.26</v>
-      </c>
       <c r="Q31" t="n">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="S31" t="n">
-        <v>3.18</v>
+        <v>2.23</v>
       </c>
       <c r="T31" t="n">
-        <v>2.48</v>
+        <v>3.65</v>
       </c>
       <c r="U31" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="X31" t="n">
-        <v>4.15</v>
+        <v>2.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.65</v>
+        <v>2.52</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.25</v>
+        <v>1.41</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.45</v>
+        <v>5.18</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.48</v>
+        <v>1.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.55</v>
+        <v>2.07</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.39</v>
+        <v>1.66</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,62 +4539,62 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.36</v>
+        <v>1.52</v>
       </c>
       <c r="M32" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="N32" t="n">
-        <v>2.59</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>2.72</v>
+        <v>2.16</v>
       </c>
       <c r="P32" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.95</v>
+        <v>6.3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="S32" t="n">
-        <v>3.04</v>
+        <v>2.55</v>
       </c>
       <c r="T32" t="n">
-        <v>2.42</v>
+        <v>3.28</v>
       </c>
       <c r="U32" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="V32" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="X32" t="n">
-        <v>3.92</v>
+        <v>2.74</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="AC32" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.58</v>
       </c>
-      <c r="AD32" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AE32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.54</v>
+        <v>2.26</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.31</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>5.5</v>
+        <v>3.92</v>
       </c>
       <c r="N34" t="n">
-        <v>8.74</v>
+        <v>3.5</v>
       </c>
       <c r="O34" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="P34" t="n">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>3.94</v>
       </c>
       <c r="R34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
         <v>1.22</v>
       </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X34" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH34" t="n">
-        <v>3.4</v>
+        <v>1.79</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="O35" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="P35" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.8</v>
+        <v>3.67</v>
       </c>
       <c r="R35" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="T35" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="U35" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V35" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="X35" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="M38" t="n">
-        <v>3.41</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="O38" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="P38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z38" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q38" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AA38" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.17</v>
+        <v>1.71</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N39" t="n">
         <v>1.95</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O39" t="n">
-        <v>2.38</v>
+        <v>4.23</v>
       </c>
       <c r="P39" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.56</v>
+        <v>2.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S39" t="n">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="T39" t="n">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="U39" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="V39" t="n">
         <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X39" t="n">
-        <v>4.81</v>
+        <v>3.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.81</v>
+        <v>1.29</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="M40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N40" t="n">
         <v>3.6</v>
       </c>
-      <c r="N40" t="n">
-        <v>1.75</v>
-      </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,19 +5767,19 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,62 +5829,62 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="M42" t="n">
-        <v>4.3</v>
+        <v>5.35</v>
       </c>
       <c r="N42" t="n">
-        <v>1.37</v>
+        <v>9.5</v>
       </c>
       <c r="O42" t="n">
-        <v>8.390000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="P42" t="n">
-        <v>2.12</v>
+        <v>2.9</v>
       </c>
       <c r="Q42" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X42" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD42" t="n">
         <v>1.95</v>
       </c>
-      <c r="R42" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AE42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.03</v>
+        <v>3.44</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,62 +6216,62 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD45" t="n">
         <v>2.15</v>
       </c>
-      <c r="M45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N45" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O45" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="T45" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AE45" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.76</v>
+        <v>2.07</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.64583333334</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="M46" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>8.5</v>
+        <v>4.7</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.6</v>
+        <v>3.76</v>
       </c>
       <c r="M47" t="n">
-        <v>2.7</v>
+        <v>3.79</v>
       </c>
       <c r="N47" t="n">
-        <v>3.05</v>
+        <v>1.85</v>
       </c>
       <c r="O47" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="S47" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="U47" t="n">
-        <v>1.14</v>
+        <v>1.46</v>
       </c>
       <c r="V47" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="W47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC47" t="n">
         <v>1.65</v>
       </c>
-      <c r="X47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.54</v>
-      </c>
       <c r="AD47" t="n">
-        <v>1.45</v>
+        <v>2.21</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="M48" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>9.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="O48" t="n">
-        <v>1.72</v>
+        <v>2.23</v>
       </c>
       <c r="P48" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>7.7</v>
+        <v>4.33</v>
       </c>
       <c r="R48" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S48" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T48" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U48" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V48" t="n">
         <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X48" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AH48" t="n">
-        <v>3.44</v>
+        <v>2.1</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="M50" t="n">
-        <v>3.69</v>
+        <v>5.2</v>
       </c>
       <c r="N50" t="n">
-        <v>3.98</v>
+        <v>7.9</v>
       </c>
       <c r="O50" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>6</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T50" t="n">
         <v>2.2</v>
       </c>
-      <c r="P50" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.38</v>
-      </c>
       <c r="U50" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="V50" t="n">
         <v>1.02</v>
       </c>
       <c r="W50" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X50" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45917.64583333334</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="51">
@@ -6949,27 +6949,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>3.51</v>
       </c>
       <c r="N51" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O51" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="P51" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.8</v>
+        <v>5.65</v>
       </c>
       <c r="R51" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S51" t="n">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="T51" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="U51" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="V51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="X51" t="n">
-        <v>4.55</v>
+        <v>3.02</v>
       </c>
       <c r="Y51" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z51" t="n">
         <v>1.68</v>
       </c>
-      <c r="Z51" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AA51" t="n">
-        <v>2.54</v>
+        <v>3.55</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.8125</v>
       </c>
     </row>
     <row r="52">
@@ -7078,27 +7078,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.76</v>
+        <v>2.24</v>
       </c>
       <c r="M52" t="n">
-        <v>3.79</v>
+        <v>3.29</v>
       </c>
       <c r="N52" t="n">
-        <v>1.85</v>
+        <v>2.72</v>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="P52" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="T52" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="V52" t="n">
         <v>1.04</v>
       </c>
       <c r="W52" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X52" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.85416666666</v>
       </c>
     </row>
     <row r="53">
@@ -7207,27 +7207,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,78 +7248,78 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="M53" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>7.9</v>
+        <v>2.65</v>
       </c>
       <c r="O53" t="n">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="P53" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>2.95</v>
       </c>
       <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X53" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y53" t="n">
         <v>1.25</v>
       </c>
-      <c r="S53" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X53" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y53" t="n">
+      <c r="Z53" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH53" t="n">
         <v>1.63</v>
       </c>
-      <c r="Z53" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AI53" t="n">
         <v>0</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.875</v>
       </c>
     </row>
     <row r="54">
@@ -7336,27 +7336,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7456,780 +7456,6 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45917.66666666666</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Bayern München</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="M55" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N55" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O55" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X55" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" s="3" t="n">
-        <v>45917.66666666666</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Botafogo</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Mirassol</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M56" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="N56" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="P56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" s="3" t="n">
-        <v>45917.8125</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Columbus Crew</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N57" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O57" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>3</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S57" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X57" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK57" s="3" t="n">
-        <v>45917.85416666666</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Houston Dynamo FC II</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="M58" t="n">
-        <v>4</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O58" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P58" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X58" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK58" s="3" t="n">
-        <v>45917.875</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>River Plate</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="M59" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="N59" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O59" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S59" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T59" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X59" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG59" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK59" s="3" t="n">
-        <v>45917.89583333334</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="N60" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="O60" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P60" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S60" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T60" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X60" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG60" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK60" s="3" t="n">
         <v>45917.9375</v>
       </c>
     </row>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK54"/>
+  <dimension ref="A1:AK61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="O5" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="P5" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.9</v>
+        <v>4.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="T5" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
         <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Y5" t="n">
         <v>2.66</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.64</v>
+        <v>5.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" t="n">
         <v>2.23</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
         <v>4.46</v>
       </c>
       <c r="R7" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="S7" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="T7" t="n">
         <v>4.53</v>
@@ -1347,16 +1347,16 @@
         <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X7" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AA7" t="n">
         <v>7.29</v>
@@ -1365,10 +1365,10 @@
         <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="N9" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="O9" t="n">
         <v>3.25</v>
@@ -1611,10 +1611,10 @@
         <v>4.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
         <v>2.33</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.19</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>3.65</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="X15" t="n">
-        <v>5.2</v>
+        <v>2.86</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.49</v>
+        <v>1.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45917.52083333334</v>
+        <v>45917.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45917.54166666666</v>
+        <v>45917.52083333334</v>
       </c>
     </row>
     <row r="20">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="P22" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="R22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.32</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45917.5625</v>
+        <v>45917.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="N23" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="O23" t="n">
         <v>9.9</v>
@@ -3426,7 +3426,7 @@
         <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
         <v>2.01</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45917.57291666666</v>
+        <v>45917.5625</v>
       </c>
     </row>
     <row r="26">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>8.74</v>
+        <v>6.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="P27" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
         <v>7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
-        <v>5.78</v>
+        <v>3.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.98</v>
+        <v>3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,19 +3961,19 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45917.58333333334</v>
+        <v>45917.57291666666</v>
       </c>
     </row>
     <row r="28">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,77 +4023,77 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.52</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.58</v>
+        <v>3.26</v>
       </c>
       <c r="O28" t="n">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.14</v>
+        <v>3.82</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>3.14</v>
+        <v>4.32</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.33</v>
+        <v>2.45</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>9.17</v>
       </c>
       <c r="O29" t="n">
-        <v>2.28</v>
+        <v>1.73</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.83</v>
+        <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="T29" t="n">
-        <v>2.49</v>
+        <v>1.98</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>3.86</v>
+        <v>5.75</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.04</v>
+        <v>3.45</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.88</v>
+        <v>3.68</v>
       </c>
       <c r="M31" t="n">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q31" t="n">
         <v>2.6</v>
       </c>
-      <c r="O31" t="n">
+      <c r="R31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA31" t="n">
         <v>3.25</v>
       </c>
-      <c r="P31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>5.18</v>
-      </c>
       <c r="AB31" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.52</v>
+        <v>2.45</v>
       </c>
       <c r="M32" t="n">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.3</v>
+        <v>3.32</v>
       </c>
       <c r="R32" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>2.55</v>
+        <v>3.04</v>
       </c>
       <c r="T32" t="n">
-        <v>3.28</v>
+        <v>2.45</v>
       </c>
       <c r="U32" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="X32" t="n">
-        <v>2.74</v>
+        <v>3.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.26</v>
+        <v>1.5</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,77 +4797,77 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.92</v>
+        <v>3.15</v>
       </c>
       <c r="N34" t="n">
         <v>3.5</v>
       </c>
       <c r="O34" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="P34" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
         <v>1.25</v>
       </c>
-      <c r="S34" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="N35" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O35" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="P35" t="n">
-        <v>2.18</v>
+        <v>2.49</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.67</v>
+        <v>3.82</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="T35" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="U35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.48</v>
       </c>
-      <c r="V35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AD35" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>4.75</v>
+        <v>4.15</v>
       </c>
       <c r="O38" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S38" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="T38" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U38" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="V38" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W38" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X38" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AI38" t="n">
         <v>1.57</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.59</v>
+        <v>2.4</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="N39" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
-        <v>4.23</v>
+        <v>3.45</v>
       </c>
       <c r="P39" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S39" t="n">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="T39" t="n">
-        <v>2.65</v>
+        <v>3.55</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V39" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W39" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="X39" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AD39" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.6</v>
+        <v>5.82</v>
       </c>
       <c r="O40" t="n">
-        <v>2.63</v>
+        <v>2.18</v>
       </c>
       <c r="P40" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.82</v>
+        <v>6</v>
       </c>
       <c r="R40" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="S40" t="n">
-        <v>3.18</v>
+        <v>2.59</v>
       </c>
       <c r="T40" t="n">
-        <v>2.48</v>
+        <v>3.26</v>
       </c>
       <c r="U40" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="X40" t="n">
-        <v>4.15</v>
+        <v>2.74</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.55</v>
+        <v>2.17</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.39</v>
+        <v>1.58</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45917.60416666666</v>
+        <v>45917.58333333334</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="M42" t="n">
-        <v>5.35</v>
+        <v>2.85</v>
       </c>
       <c r="N42" t="n">
-        <v>9.5</v>
+        <v>2.3</v>
       </c>
       <c r="O42" t="n">
-        <v>1.68</v>
+        <v>4.05</v>
       </c>
       <c r="P42" t="n">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="Q42" t="n">
-        <v>8.25</v>
+        <v>3.24</v>
       </c>
       <c r="R42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U42" t="n">
         <v>1.21</v>
       </c>
-      <c r="S42" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.65</v>
-      </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="W42" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="X42" t="n">
-        <v>5.1</v>
+        <v>2.45</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.49</v>
+        <v>3.05</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.6</v>
+        <v>1.37</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.69</v>
+        <v>1.12</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AH42" t="n">
-        <v>3.44</v>
+        <v>1.31</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45917.625</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="M45" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="N45" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O45" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="P45" t="n">
-        <v>2.34</v>
+        <v>1.74</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.5</v>
+        <v>6.08</v>
       </c>
       <c r="R45" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="S45" t="n">
-        <v>3.2</v>
+        <v>2.09</v>
       </c>
       <c r="T45" t="n">
-        <v>2.38</v>
+        <v>4.15</v>
       </c>
       <c r="U45" t="n">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="V45" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="W45" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="X45" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.66</v>
+        <v>3</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.17</v>
+        <v>1.35</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.68</v>
+        <v>6.35</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.64</v>
+        <v>2.61</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45917.64583333334</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>8.5</v>
       </c>
       <c r="O46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
         <v>2.3</v>
       </c>
-      <c r="U46" t="n">
+      <c r="Z46" t="n">
         <v>1.55</v>
       </c>
-      <c r="V46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X46" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AA46" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.76</v>
+        <v>2.6</v>
       </c>
       <c r="M47" t="n">
-        <v>3.79</v>
+        <v>2.7</v>
       </c>
       <c r="N47" t="n">
-        <v>1.85</v>
+        <v>3.05</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="P47" t="n">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.5</v>
+        <v>3.86</v>
       </c>
       <c r="R47" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="T47" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="U47" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="V47" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="W47" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="X47" t="n">
-        <v>3.92</v>
+        <v>2.1</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.87</v>
+        <v>3.34</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.93</v>
+        <v>1.24</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.85</v>
+        <v>7.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.41</v>
+        <v>1.08</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.65</v>
+        <v>2.54</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.21</v>
+        <v>1.45</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.60416666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.69</v>
+        <v>1.31</v>
       </c>
       <c r="M48" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="N48" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="O48" t="n">
-        <v>2.23</v>
+        <v>1.68</v>
       </c>
       <c r="P48" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="R48" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S48" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T48" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U48" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V48" t="n">
         <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X48" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.1</v>
+        <v>3.44</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45917.66666666666</v>
+        <v>45917.625</v>
       </c>
     </row>
     <row r="51">
@@ -6949,27 +6949,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="M51" t="n">
-        <v>3.51</v>
+        <v>3.85</v>
       </c>
       <c r="N51" t="n">
-        <v>5.1</v>
+        <v>4.15</v>
       </c>
       <c r="O51" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="P51" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X51" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z51" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q51" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X51" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AA51" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.69</v>
+        <v>2.17</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45917.8125</v>
+        <v>45917.64583333334</v>
       </c>
     </row>
     <row r="52">
@@ -7078,27 +7078,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.24</v>
+        <v>1.33</v>
       </c>
       <c r="M52" t="n">
-        <v>3.29</v>
+        <v>5.2</v>
       </c>
       <c r="N52" t="n">
-        <v>2.72</v>
+        <v>7.9</v>
       </c>
       <c r="O52" t="n">
-        <v>2.85</v>
+        <v>1.78</v>
       </c>
       <c r="P52" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R52" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S52" t="n">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="T52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X52" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z52" t="n">
         <v>2.25</v>
       </c>
-      <c r="U52" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X52" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AA52" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45917.85416666666</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="53">
@@ -7207,27 +7207,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,78 +7248,78 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.07</v>
+        <v>3.76</v>
       </c>
       <c r="M53" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O53" t="n">
         <v>4</v>
       </c>
-      <c r="N53" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q53" t="n">
         <v>2.5</v>
       </c>
-      <c r="P53" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2.95</v>
-      </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T53" t="n">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="U53" t="n">
-        <v>1.92</v>
+        <v>1.46</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W53" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="X53" t="n">
-        <v>7.1</v>
+        <v>3.92</v>
       </c>
       <c r="Y53" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH53" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z53" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AI53" t="n">
         <v>0</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45917.875</v>
+        <v>45917.66666666666</v>
       </c>
     </row>
     <row r="54">
@@ -7336,126 +7336,1029 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Raja Casablanca</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>FAR Rabat</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="3" t="n">
+        <v>45917.66666666666</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M55" t="n">
+        <v>4</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X55" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="3" t="n">
+        <v>45917.66666666666</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Bayern München</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X56" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="3" t="n">
+        <v>45917.66666666666</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N57" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>5</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X57" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="3" t="n">
+        <v>45917.8125</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X58" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3" t="n">
+        <v>45917.85416666666</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC II</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M59" t="n">
+        <v>4</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P59" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X59" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="3" t="n">
+        <v>45917.875</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O60" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X60" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="3" t="n">
+        <v>45917.89583333334</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Real Salt Lake</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L54" t="n">
+      <c r="L61" t="n">
         <v>2.5</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M61" t="n">
         <v>3.31</v>
       </c>
-      <c r="N54" t="n">
+      <c r="N61" t="n">
         <v>2.39</v>
       </c>
-      <c r="O54" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q54" t="n">
+      <c r="O61" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P61" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q61" t="n">
         <v>3.1</v>
       </c>
-      <c r="R54" t="n">
+      <c r="R61" t="n">
         <v>1.3</v>
       </c>
-      <c r="S54" t="n">
+      <c r="S61" t="n">
         <v>3.2</v>
       </c>
-      <c r="T54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V54" t="n">
+      <c r="T61" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V61" t="n">
         <v>1.03</v>
       </c>
-      <c r="W54" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X54" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="Y54" t="n">
+      <c r="W61" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X61" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y61" t="n">
         <v>1.79</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="Z61" t="n">
         <v>1.91</v>
       </c>
-      <c r="AA54" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD54" t="n">
+      <c r="AA61" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD61" t="n">
         <v>2.21</v>
       </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" s="3" t="n">
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3" t="n">
         <v>45917.9375</v>
       </c>
     </row>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1056,28 +1056,28 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="M5" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="N5" t="n">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="P5" t="n">
         <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.88</v>
+        <v>4.96</v>
       </c>
       <c r="R5" t="n">
         <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="T5" t="n">
         <v>3.74</v>
@@ -1092,19 +1092,19 @@
         <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Y5" t="n">
         <v>2.66</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AA5" t="n">
         <v>5.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AC5" t="n">
         <v>2.23</v>
@@ -1126,7 +1126,7 @@
         <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
         <v>3.34</v>
@@ -1332,10 +1332,10 @@
         <v>4.46</v>
       </c>
       <c r="R7" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="S7" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
         <v>4.53</v>
@@ -1347,13 +1347,13 @@
         <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X7" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="Z7" t="n">
         <v>1.27</v>
@@ -1368,7 +1368,7 @@
         <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AH7" t="n">
         <v>1.46</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
         <v>2.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R9" t="n">
         <v>1.26</v>
@@ -1596,16 +1596,16 @@
         <v>3.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>4.4</v>
@@ -1614,19 +1614,19 @@
         <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
         <v>2.57</v>
@@ -1725,31 +1725,31 @@
         <v>2.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X10" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="Z10" t="n">
         <v>1.49</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AC10" t="n">
         <v>2.32</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="M14" t="n">
-        <v>3.71</v>
+        <v>3.53</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>2.87</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
         <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.19</v>
+        <v>3.36</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="T14" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="U14" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
         <v>1.36</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>9.199999999999999</v>
+        <v>2.06</v>
       </c>
       <c r="M23" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.2</v>
+        <v>2.98</v>
       </c>
       <c r="O23" t="n">
-        <v>9.9</v>
+        <v>2.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.66</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.59</v>
+        <v>3.61</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="U23" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.49</v>
+        <v>2.06</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="N28" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="O28" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="Q28" t="n">
         <v>3.82</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="T28" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="U28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.55</v>
       </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X28" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>9.17</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>4.41</v>
+        <v>3.45</v>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="T31" t="n">
-        <v>2.65</v>
+        <v>3.65</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="X31" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N32" t="n">
         <v>2.45</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.75</v>
-      </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="R32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W32" t="n">
         <v>1.3</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.23</v>
-      </c>
       <c r="X32" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.75</v>
+        <v>3.33</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="M34" t="n">
-        <v>3.15</v>
+        <v>3.74</v>
       </c>
       <c r="N34" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="P34" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="T34" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="U34" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V34" t="n">
         <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X34" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Z34" t="n">
         <v>2.07</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AB34" t="n">
         <v>1.42</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="M35" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="N35" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>7</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH35" t="n">
         <v>3.45</v>
       </c>
-      <c r="O35" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.46</v>
+        <v>2.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="O36" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.43</v>
+        <v>3.32</v>
       </c>
       <c r="R36" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="T36" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="U36" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="V36" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="X36" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="M37" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="O37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S37" t="n">
         <v>3.25</v>
       </c>
-      <c r="P37" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T37" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="U37" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="V37" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="X37" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N38" t="n">
-        <v>4.15</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="P38" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="R38" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="S38" t="n">
-        <v>3.22</v>
+        <v>2.57</v>
       </c>
       <c r="T38" t="n">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="U38" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="V38" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="X38" t="n">
-        <v>3.55</v>
+        <v>2.76</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.78</v>
+        <v>2.19</v>
       </c>
       <c r="AD38" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI39" t="n">
         <v>2.4</v>
       </c>
-      <c r="M39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.57</v>
+        <v>3.46</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="N40" t="n">
-        <v>5.82</v>
+        <v>1.89</v>
       </c>
       <c r="O40" t="n">
-        <v>2.18</v>
+        <v>3.9</v>
       </c>
       <c r="P40" t="n">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>2.43</v>
       </c>
       <c r="R40" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="T40" t="n">
-        <v>3.26</v>
+        <v>2.26</v>
       </c>
       <c r="U40" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="X40" t="n">
-        <v>2.74</v>
+        <v>4.33</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.6</v>
+        <v>2.32</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.2</v>
+        <v>2.33</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.17</v>
+        <v>1.55</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.58</v>
+        <v>2.41</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.08</v>
+        <v>1.27</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="M41" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="O41" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="P41" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S41" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="T41" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U41" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V41" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X41" t="n">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.3</v>
+        <v>8.5</v>
       </c>
       <c r="M42" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="N42" t="n">
-        <v>2.3</v>
+        <v>1.37</v>
       </c>
       <c r="O42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA42" t="n">
         <v>4.05</v>
       </c>
-      <c r="P42" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AB42" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>8.5</v>
+        <v>2.15</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="N43" t="n">
-        <v>1.37</v>
+        <v>3.9</v>
       </c>
       <c r="O43" t="n">
-        <v>8.390000000000001</v>
+        <v>2.71</v>
       </c>
       <c r="P43" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.95</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="S43" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="T43" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y43" t="n">
         <v>3</v>
       </c>
-      <c r="U43" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.88</v>
-      </c>
       <c r="Z43" t="n">
-        <v>1.82</v>
+        <v>1.31</v>
       </c>
       <c r="AA43" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.03</v>
+        <v>1.77</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M45" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N45" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="O45" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="P45" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q45" t="n">
-        <v>6.08</v>
+        <v>3.8</v>
       </c>
       <c r="R45" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="S45" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="T45" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="U45" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="V45" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="W45" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="X45" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Y45" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AA45" t="n">
-        <v>6.35</v>
+        <v>7.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M46" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N46" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="M47" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N47" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="O47" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="P47" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="R47" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="S47" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="T47" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="U47" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="V47" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="W47" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="X47" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Y47" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AA47" t="n">
-        <v>7.5</v>
+        <v>5.78</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.76</v>
+        <v>1.64</v>
       </c>
       <c r="M53" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="P53" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="R53" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T53" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U53" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="V53" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W53" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X53" t="n">
-        <v>3.92</v>
+        <v>4.55</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AC53" t="n">
         <v>1.65</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.64</v>
+        <v>3.76</v>
       </c>
       <c r="M55" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O55" t="n">
         <v>4</v>
       </c>
-      <c r="N55" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O55" t="n">
-        <v>2.1</v>
-      </c>
       <c r="P55" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="R55" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S55" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U55" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="V55" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W55" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X55" t="n">
-        <v>4.55</v>
+        <v>3.92</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.54</v>
+        <v>2.85</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AC55" t="n">
         <v>1.65</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="M57" t="n">
-        <v>3.51</v>
+        <v>3.64</v>
       </c>
       <c r="N57" t="n">
-        <v>5.1</v>
+        <v>5.13</v>
       </c>
       <c r="O57" t="n">
         <v>2.25</v>
       </c>
       <c r="P57" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R57" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S57" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="T57" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U57" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V57" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W57" t="n">
         <v>1.31</v>
       </c>
       <c r="X57" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA57" t="n">
         <v>3.85</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AH57" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7896,31 +7896,31 @@
         <v>2.24</v>
       </c>
       <c r="M58" t="n">
-        <v>3.29</v>
+        <v>3.66</v>
       </c>
       <c r="N58" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="O58" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P58" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R58" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S58" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="T58" t="n">
         <v>2.25</v>
       </c>
       <c r="U58" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="V58" t="n">
         <v>1.04</v>
@@ -7929,19 +7929,19 @@
         <v>1.24</v>
       </c>
       <c r="X58" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC58" t="n">
         <v>1.57</v>
@@ -7963,7 +7963,7 @@
         <v>1.4</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -8022,22 +8022,22 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="N59" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="O59" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="P59" t="n">
         <v>2.7</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="M61" t="n">
-        <v>3.31</v>
+        <v>3.55</v>
       </c>
       <c r="N61" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="O61" t="n">
         <v>3.25</v>
       </c>
       <c r="P61" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R61" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S61" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="T61" t="n">
         <v>2.52</v>
       </c>
       <c r="U61" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="V61" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W61" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X61" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AD61" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>7.29</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>16</v>
       </c>
       <c r="O7" t="n">
-        <v>3.34</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.46</v>
+        <v>13.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>4.53</v>
+        <v>2.69</v>
       </c>
       <c r="U7" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.29</v>
+        <v>2.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.46</v>
+        <v>4.2</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>1.96</v>
       </c>
       <c r="M8" t="n">
-        <v>5.5</v>
+        <v>2.77</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.58</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1.38</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AA8" t="n">
-        <v>2.83</v>
+        <v>5.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.45</v>
+        <v>1.68</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3</v>
+        <v>1.77</v>
       </c>
       <c r="O10" t="n">
-        <v>2.57</v>
+        <v>4.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.75</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="T10" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="X10" t="n">
-        <v>2.35</v>
+        <v>2.86</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.06</v>
+        <v>3.82</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.91</v>
+        <v>1.17</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.4</v>
+        <v>1.96</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.53</v>
       </c>
       <c r="N12" t="n">
-        <v>1.77</v>
+        <v>2.87</v>
       </c>
       <c r="O12" t="n">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.38</v>
+        <v>3.36</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>2.55</v>
+        <v>3.74</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>2.19</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>2.86</v>
+        <v>5.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.82</v>
+        <v>2.18</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.21</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.74</v>
+        <v>2.54</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.66</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,62 +3120,62 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
         <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>3.43</v>
+        <v>2.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="T21" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD21" t="n">
         <v>2.12</v>
       </c>
-      <c r="AA21" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AE21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>11</v>
+        <v>2.06</v>
       </c>
       <c r="M25" t="n">
-        <v>6.25</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.18</v>
       </c>
-      <c r="O25" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.1</v>
-      </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.41</v>
       </c>
-      <c r="Z25" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AC25" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>4.25</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="O28" t="n">
-        <v>2.35</v>
+        <v>3.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.82</v>
+        <v>3.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.31</v>
+        <v>3.33</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S31" t="n">
         <v>2.88</v>
       </c>
-      <c r="M31" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.25</v>
-      </c>
       <c r="T31" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="U31" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="X31" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.62</v>
+        <v>1.28</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>5.75</v>
       </c>
       <c r="N32" t="n">
-        <v>2.45</v>
+        <v>9.6</v>
       </c>
       <c r="O32" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="P32" t="n">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="T32" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.3</v>
       </c>
-      <c r="X32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="N33" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="O33" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="Q33" t="n">
         <v>3.82</v>
       </c>
       <c r="R33" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="T33" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="U33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.55</v>
       </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X33" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="M34" t="n">
-        <v>3.74</v>
+        <v>3.39</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>3.11</v>
       </c>
       <c r="O34" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P34" t="n">
         <v>2.3</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.33</v>
-      </c>
       <c r="Q34" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>3.04</v>
+        <v>3.18</v>
       </c>
       <c r="T34" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="V34" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>3.82</v>
+        <v>4.15</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.25</v>
       </c>
-      <c r="M35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>7</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH35" t="n">
-        <v>3.45</v>
+        <v>1.27</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5055,25 +5055,25 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="N36" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="P36" t="n">
         <v>2.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
         <v>3.04</v>
@@ -5091,13 +5091,13 @@
         <v>1.23</v>
       </c>
       <c r="X36" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="Y36" t="n">
         <v>1.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA36" t="n">
         <v>2.75</v>
@@ -5125,7 +5125,7 @@
         <v>1.44</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>3.74</v>
       </c>
       <c r="N37" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O37" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="T37" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="U37" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V37" t="n">
         <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X37" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Z37" t="n">
         <v>2.07</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AB37" t="n">
         <v>1.42</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.52</v>
+        <v>2.88</v>
       </c>
       <c r="M38" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
-        <v>2.18</v>
+        <v>3.45</v>
       </c>
       <c r="P38" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="Q38" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="R38" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S38" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="T38" t="n">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="U38" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W38" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="X38" t="n">
-        <v>2.76</v>
+        <v>2.3</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.27</v>
+        <v>1.44</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.68</v>
+        <v>1.52</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
-        <v>4.41</v>
+        <v>2.18</v>
       </c>
       <c r="P39" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="S39" t="n">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="T39" t="n">
-        <v>2.65</v>
+        <v>3.28</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="V39" t="n">
         <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="X39" t="n">
-        <v>3.6</v>
+        <v>2.76</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.73</v>
+        <v>2.19</v>
       </c>
       <c r="AD39" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.26</v>
+        <v>2.27</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.46</v>
+        <v>1.9</v>
       </c>
       <c r="M40" t="n">
-        <v>3.72</v>
+        <v>3.15</v>
       </c>
       <c r="N40" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
       <c r="P40" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.43</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="T40" t="n">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="U40" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="V40" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X40" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="M45" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="N45" t="n">
-        <v>3.05</v>
+        <v>7.2</v>
       </c>
       <c r="O45" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>3.34</v>
+        <v>2.3</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AA45" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.44</v>
+        <v>3.3</v>
       </c>
       <c r="M46" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q46" t="n">
         <v>3.6</v>
       </c>
-      <c r="N46" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="M47" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N47" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="O47" t="n">
-        <v>3.8</v>
+        <v>2.71</v>
       </c>
       <c r="P47" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="S47" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="T47" t="n">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="U47" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V47" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W47" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="X47" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AA47" t="n">
-        <v>5.78</v>
+        <v>6.25</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,77 +7119,77 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.33</v>
+        <v>3.76</v>
       </c>
       <c r="M52" t="n">
-        <v>5.2</v>
+        <v>3.79</v>
       </c>
       <c r="N52" t="n">
-        <v>7.9</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
-        <v>1.78</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="Q52" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="R52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X52" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH52" t="n">
         <v>1.25</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X52" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>3.1</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="N53" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="O53" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="P53" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="R53" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S53" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="T53" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="V53" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W53" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X53" t="n">
-        <v>4.55</v>
+        <v>5.6</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,77 +7506,77 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.76</v>
+        <v>1.69</v>
       </c>
       <c r="M55" t="n">
-        <v>3.79</v>
+        <v>4.2</v>
       </c>
       <c r="N55" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>2.23</v>
       </c>
       <c r="P55" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="R55" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T55" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U55" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="V55" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W55" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X55" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
         <v>1.22</v>
       </c>
-      <c r="X55" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH55" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45917.45833333334</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.46</v>
+        <v>4.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="T6" t="n">
-        <v>4.53</v>
+        <v>3.74</v>
       </c>
       <c r="U6" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.29</v>
+        <v>5.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45917.45833333334</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>16</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.58</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.5</v>
+        <v>4.39</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="T7" t="n">
-        <v>2.69</v>
+        <v>4.3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="X7" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>1.29</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.83</v>
+        <v>6.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.2</v>
+        <v>1.46</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,40 +1572,40 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="N9" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S9" t="n">
         <v>3.3</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.34</v>
-      </c>
       <c r="T9" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
         <v>4.4</v>
@@ -1614,19 +1614,19 @@
         <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.45</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AD9" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.4</v>
+        <v>2.16</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.71</v>
       </c>
       <c r="N10" t="n">
-        <v>1.77</v>
+        <v>2.58</v>
       </c>
       <c r="O10" t="n">
-        <v>4.75</v>
+        <v>2.49</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>2.27</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>2.86</v>
+        <v>5.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.82</v>
+        <v>2.07</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>2.45</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45917.47916666666</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45917.47916666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,62 +2991,62 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
         <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>3.43</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="X20" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD20" t="n">
         <v>2.12</v>
       </c>
-      <c r="AA20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AE20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.59</v>
       </c>
       <c r="N21" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="P21" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V21" t="n">
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="N25" t="n">
-        <v>2.98</v>
+        <v>1.2</v>
       </c>
       <c r="O25" t="n">
-        <v>2.55</v>
+        <v>7.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.61</v>
+        <v>1.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.57</v>
+        <v>2.16</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>3.85</v>
+        <v>5.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.78</v>
+        <v>2.88</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>2.26</v>
+        <v>3.2</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.85</v>
+        <v>3.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="S31" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="T31" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="U31" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="X31" t="n">
-        <v>3.55</v>
+        <v>2.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.83</v>
+        <v>2.56</v>
       </c>
       <c r="Z31" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,58 +4539,58 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="M32" t="n">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>1.67</v>
+        <v>2.26</v>
       </c>
       <c r="P32" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>4.85</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="U32" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="X32" t="n">
-        <v>5.75</v>
+        <v>3.55</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.12</v>
+        <v>2.88</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AD32" t="n">
         <v>2</v>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.4</v>
+        <v>1.87</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AJ32" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.91</v>
+        <v>1.28</v>
       </c>
       <c r="M33" t="n">
-        <v>3.95</v>
+        <v>5.75</v>
       </c>
       <c r="N33" t="n">
-        <v>3.45</v>
+        <v>9.6</v>
       </c>
       <c r="O33" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="P33" t="n">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.82</v>
+        <v>7</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S33" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="T33" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="V33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X33" t="n">
-        <v>4.6</v>
+        <v>5.75</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="M34" t="n">
-        <v>3.39</v>
+        <v>3.23</v>
       </c>
       <c r="N34" t="n">
-        <v>3.11</v>
+        <v>2.59</v>
       </c>
       <c r="O34" t="n">
-        <v>2.61</v>
+        <v>2.9</v>
       </c>
       <c r="P34" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.82</v>
+        <v>2.95</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U34" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W34" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="X34" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AC34" t="n">
         <v>1.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>2.59</v>
+        <v>3.5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.99</v>
+        <v>2.38</v>
       </c>
       <c r="P36" t="n">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="T36" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U36" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W36" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X36" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AA36" t="n">
         <v>2.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="M37" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="N37" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="O37" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="P37" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="T37" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="U37" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W37" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X37" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="AB37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.42</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.9</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="M38" t="n">
-        <v>2.58</v>
+        <v>3.95</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="O38" t="n">
-        <v>3.45</v>
+        <v>2.35</v>
       </c>
       <c r="P38" t="n">
-        <v>1.79</v>
+        <v>2.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="R38" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>2.25</v>
+        <v>3.42</v>
       </c>
       <c r="T38" t="n">
-        <v>3.65</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="V38" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB38" t="n">
         <v>1.55</v>
       </c>
-      <c r="X38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AC38" t="n">
-        <v>2.07</v>
+        <v>1.48</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="M39" t="n">
-        <v>3.41</v>
+        <v>3.74</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O39" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="P39" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="R39" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
-        <v>2.57</v>
+        <v>3.04</v>
       </c>
       <c r="T39" t="n">
-        <v>3.28</v>
+        <v>2.6</v>
       </c>
       <c r="U39" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="V39" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W39" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="X39" t="n">
-        <v>2.76</v>
+        <v>3.82</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.59</v>
+        <v>2.12</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="M40" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="N40" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="O40" t="n">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="P40" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="T40" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="U40" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X40" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>8.5</v>
+        <v>1.47</v>
       </c>
       <c r="M42" t="n">
-        <v>4.3</v>
+        <v>3.78</v>
       </c>
       <c r="N42" t="n">
-        <v>1.37</v>
+        <v>7.8</v>
       </c>
       <c r="O42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -6096,19 +6096,19 @@
         <v>3.05</v>
       </c>
       <c r="O44" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P44" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="R44" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="S44" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="T44" t="n">
         <v>4.6</v>
@@ -6117,7 +6117,7 @@
         <v>1.14</v>
       </c>
       <c r="V44" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="W44" t="n">
         <v>1.65</v>
@@ -6126,16 +6126,16 @@
         <v>2.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>3.34</v>
+        <v>3.41</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AA44" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AC44" t="n">
         <v>2.54</v>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,62 +6216,62 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>5</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.44</v>
       </c>
-      <c r="M45" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N45" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
       <c r="AE45" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.3</v>
+        <v>8.5</v>
       </c>
       <c r="M46" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="N46" t="n">
-        <v>2.3</v>
+        <v>1.37</v>
       </c>
       <c r="O46" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="P46" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="S46" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="T46" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="U46" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V46" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W46" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="X46" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC46" t="n">
         <v>2.45</v>
       </c>
-      <c r="Y46" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD46" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="M47" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N47" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="O47" t="n">
-        <v>2.71</v>
+        <v>3.85</v>
       </c>
       <c r="P47" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>3.59</v>
       </c>
       <c r="R47" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="S47" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T47" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="U47" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V47" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="W47" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="X47" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Y47" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AA47" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="M48" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="N48" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="P48" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R48" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S48" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T48" t="n">
         <v>2.1</v>
       </c>
       <c r="U48" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V48" t="n">
         <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X48" t="n">
         <v>5.1</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
         <v>1.75</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AH48" t="n">
         <v>3.44</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6990,16 +6990,16 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="M51" t="n">
-        <v>3.85</v>
+        <v>3.69</v>
       </c>
       <c r="N51" t="n">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="O51" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="P51" t="n">
         <v>2.21</v>
@@ -7008,43 +7008,43 @@
         <v>4.3</v>
       </c>
       <c r="R51" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S51" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="T51" t="n">
         <v>2.38</v>
       </c>
       <c r="U51" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V51" t="n">
         <v>1.04</v>
       </c>
       <c r="W51" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X51" t="n">
-        <v>4.36</v>
+        <v>4.15</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AB51" t="n">
         <v>1.48</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH51" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="M53" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="N53" t="n">
-        <v>7.9</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="P53" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="R53" t="n">
         <v>1.25</v>
       </c>
       <c r="S53" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="T53" t="n">
         <v>2.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V53" t="n">
         <v>1.02</v>
       </c>
       <c r="W53" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X53" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AA53" t="n">
         <v>2.35</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AH53" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="N54" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="O54" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="P54" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="R54" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S54" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="T54" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U54" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="V54" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W54" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X54" t="n">
-        <v>4.55</v>
+        <v>5.6</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,77 +7506,77 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.69</v>
+        <v>3.76</v>
       </c>
       <c r="M55" t="n">
-        <v>4.2</v>
+        <v>3.79</v>
       </c>
       <c r="N55" t="n">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="O55" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="P55" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q55" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q55" t="n">
-        <v>4.33</v>
-      </c>
       <c r="R55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X55" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH55" t="n">
         <v>1.25</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X55" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>2.1</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7764,34 +7764,34 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="M57" t="n">
-        <v>3.64</v>
+        <v>3.51</v>
       </c>
       <c r="N57" t="n">
-        <v>5.13</v>
+        <v>5.1</v>
       </c>
       <c r="O57" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="P57" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q57" t="n">
-        <v>6</v>
+        <v>4.84</v>
       </c>
       <c r="R57" t="n">
         <v>1.4</v>
       </c>
       <c r="S57" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="T57" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U57" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V57" t="n">
         <v>1.02</v>
@@ -7800,25 +7800,25 @@
         <v>1.31</v>
       </c>
       <c r="X57" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.85</v>
+        <v>3.48</v>
       </c>
       <c r="AB57" t="n">
         <v>1.24</v>
       </c>
       <c r="AC57" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AH57" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7896,52 +7896,52 @@
         <v>2.24</v>
       </c>
       <c r="M58" t="n">
-        <v>3.66</v>
+        <v>3.29</v>
       </c>
       <c r="N58" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="O58" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P58" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R58" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S58" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T58" t="n">
         <v>2.25</v>
       </c>
       <c r="U58" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="V58" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W58" t="n">
         <v>1.24</v>
       </c>
       <c r="X58" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC58" t="n">
         <v>1.57</v>
@@ -8028,7 +8028,7 @@
         <v>3.95</v>
       </c>
       <c r="N59" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="O59" t="n">
         <v>2.51</v>
@@ -8046,10 +8046,10 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="U59" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -8070,13 +8070,13 @@
         <v>1.7</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AD59" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="M61" t="n">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="N61" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="O61" t="n">
         <v>3.25</v>
       </c>
       <c r="P61" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R61" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S61" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="T61" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="U61" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="V61" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W61" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X61" t="n">
         <v>4.2</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AD61" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>1.3</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.18</v>
+        <v>1.96</v>
       </c>
       <c r="M5" t="n">
-        <v>5.7</v>
+        <v>2.77</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.1</v>
+        <v>4.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="T5" t="n">
-        <v>2.58</v>
+        <v>3.74</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>3.58</v>
+        <v>2.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.8</v>
+        <v>2.81</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC5" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AH5" t="n">
-        <v>3.7</v>
+        <v>1.69</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.16</v>
+        <v>1.85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6.65</v>
+        <v>2.65</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45917.45833333334</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45917.45833333334</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>1.18</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>5.7</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>13</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.39</v>
+        <v>12.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.71</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>1.97</v>
+        <v>2.93</v>
       </c>
       <c r="T7" t="n">
-        <v>4.3</v>
+        <v>2.58</v>
       </c>
       <c r="U7" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>1.95</v>
+        <v>3.58</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.29</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.55</v>
+        <v>2.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.46</v>
+        <v>3.7</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45917.45833333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45917.45833333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45917.47916666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45917.47916666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45917.47916666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45917.47916666666</v>
@@ -2739,7 +2739,7 @@
         <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="O18" t="n">
         <v>3.7</v>
@@ -2806,10 +2806,10 @@
         <v>1.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45917.5</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.59</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.76</v>
+        <v>2.49</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V20" t="n">
         <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9.199999999999999</v>
+        <v>2.17</v>
       </c>
       <c r="M25" t="n">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.2</v>
+        <v>3.05</v>
       </c>
       <c r="O25" t="n">
-        <v>7.5</v>
+        <v>2.68</v>
       </c>
       <c r="P25" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.6</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.25</v>
       </c>
-      <c r="S25" t="n">
-        <v>4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.11</v>
-      </c>
       <c r="X25" t="n">
-        <v>5.15</v>
+        <v>3.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.77</v>
+        <v>1.49</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.57</v>
+        <v>6.8</v>
       </c>
       <c r="O26" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.62</v>
+        <v>2.9</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.88</v>
+        <v>2.75</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>6.8</v>
+        <v>3.57</v>
       </c>
       <c r="O27" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="P27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T27" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q27" t="n">
-        <v>7</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.62</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.52</v>
+        <v>3.69</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>1.85</v>
       </c>
       <c r="O29" t="n">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.81</v>
+        <v>2.6</v>
       </c>
       <c r="R29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.35</v>
       </c>
       <c r="V29" t="n">
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.27</v>
+        <v>1.29</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q31" t="n">
         <v>2.88</v>
       </c>
-      <c r="M31" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.7</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="X31" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>5</v>
+        <v>3.32</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.37</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.78</v>
+        <v>2.36</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>2.59</v>
       </c>
       <c r="O32" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.85</v>
+        <v>2.95</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="U32" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
         <v>1.23</v>
       </c>
       <c r="X32" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.28</v>
+        <v>1.88</v>
       </c>
       <c r="M33" t="n">
-        <v>5.75</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="O33" t="n">
-        <v>1.67</v>
+        <v>2.37</v>
       </c>
       <c r="P33" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>7</v>
+        <v>4.03</v>
       </c>
       <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.2</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X33" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH33" t="n">
-        <v>3.4</v>
+        <v>1.96</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.36</v>
+        <v>1.99</v>
       </c>
       <c r="M34" t="n">
-        <v>3.23</v>
+        <v>3.39</v>
       </c>
       <c r="N34" t="n">
-        <v>2.59</v>
+        <v>3.11</v>
       </c>
       <c r="O34" t="n">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="T34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA34" t="n">
         <v>2.45</v>
       </c>
-      <c r="U34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AB34" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC34" t="n">
         <v>1.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.46</v>
+        <v>1.78</v>
       </c>
       <c r="M35" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.89</v>
       </c>
-      <c r="O35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.59</v>
-      </c>
       <c r="Z35" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.41</v>
+        <v>1.99</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
       <c r="N36" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="P36" t="n">
-        <v>2.34</v>
+        <v>2.03</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>6.81</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="T36" t="n">
-        <v>2.48</v>
+        <v>3.28</v>
       </c>
       <c r="U36" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="V36" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="X36" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.75</v>
+        <v>4.15</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.66</v>
+        <v>2.19</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.77</v>
+        <v>2.27</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,62 +5184,62 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="M37" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD37" t="n">
         <v>2.45</v>
       </c>
-      <c r="O37" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="M38" t="n">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="N38" t="n">
-        <v>3.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="P38" t="n">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.82</v>
+        <v>7</v>
       </c>
       <c r="R38" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S38" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="T38" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="U38" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="V38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X38" t="n">
-        <v>4.6</v>
+        <v>5.34</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.82</v>
+        <v>2.88</v>
       </c>
       <c r="M39" t="n">
-        <v>3.74</v>
+        <v>2.58</v>
       </c>
       <c r="N39" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X39" t="n">
         <v>2.3</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.82</v>
-      </c>
       <c r="Y39" t="n">
-        <v>1.76</v>
+        <v>2.56</v>
       </c>
       <c r="Z39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC39" t="n">
         <v>2.07</v>
       </c>
-      <c r="AA39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD39" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,62 +5571,62 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.99</v>
+        <v>3.6</v>
       </c>
       <c r="M40" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N40" t="n">
-        <v>3.11</v>
+        <v>1.85</v>
       </c>
       <c r="O40" t="n">
-        <v>2.61</v>
+        <v>3.46</v>
       </c>
       <c r="P40" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T40" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD40" t="n">
         <v>2.32</v>
       </c>
-      <c r="U40" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X40" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.29</v>
-      </c>
       <c r="AE40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.73</v>
+        <v>1.21</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="M42" t="n">
-        <v>3.78</v>
+        <v>2.8</v>
       </c>
       <c r="N42" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.3</v>
+        <v>3.21</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.15</v>
+        <v>8.5</v>
       </c>
       <c r="M45" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>3.9</v>
+        <v>1.37</v>
       </c>
       <c r="O45" t="n">
-        <v>2.71</v>
+        <v>7.8</v>
       </c>
       <c r="P45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z45" t="n">
         <v>1.82</v>
       </c>
-      <c r="Q45" t="n">
-        <v>5</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T45" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AA45" t="n">
-        <v>6.25</v>
+        <v>4.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.77</v>
+        <v>1.03</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>8.5</v>
+        <v>1.47</v>
       </c>
       <c r="M46" t="n">
-        <v>4.3</v>
+        <v>3.78</v>
       </c>
       <c r="N46" t="n">
-        <v>1.37</v>
+        <v>7.8</v>
       </c>
       <c r="O46" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="M53" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O53" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="P53" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="R53" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S53" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T53" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X53" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z53" t="n">
         <v>2.2</v>
       </c>
-      <c r="U53" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X53" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AA53" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7764,16 +7764,16 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M57" t="n">
-        <v>3.51</v>
+        <v>3.7</v>
       </c>
       <c r="N57" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="O57" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="P57" t="n">
         <v>2.06</v>
@@ -7782,43 +7782,43 @@
         <v>4.84</v>
       </c>
       <c r="R57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U57" t="n">
         <v>1.4</v>
       </c>
-      <c r="S57" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V57" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W57" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X57" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.48</v>
+        <v>3.84</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC57" t="n">
         <v>2.02</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>

--- a/jogos_2025-09-17.xlsx
+++ b/jogos_2025-09-17.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -871,10 +871,10 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45917.4375</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45917.4375</v>
@@ -1074,19 +1074,19 @@
         <v>4.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S5" t="n">
         <v>2.15</v>
       </c>
       <c r="T5" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
         <v>1.55</v>
@@ -1104,10 +1104,10 @@
         <v>5.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AD5" t="n">
         <v>1.61</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AI5" t="n">
         <v>1.85</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45917.45833333334</v>
@@ -1323,10 +1323,10 @@
         <v>13</v>
       </c>
       <c r="O7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
         <v>12.1</v>
@@ -1338,19 +1338,19 @@
         <v>2.93</v>
       </c>
       <c r="T7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="Y7" t="n">
         <v>1.8</v>
@@ -1359,16 +1359,16 @@
         <v>1.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.95</v>
+        <v>2.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AH7" t="n">
         <v>3.7</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45917.45833333334</v>
@@ -1581,7 +1581,7 @@
         <v>2.21</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
         <v>2.25</v>
@@ -1590,7 +1590,7 @@
         <v>2.85</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
         <v>3.3</v>
@@ -1599,19 +1599,19 @@
         <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>4.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z9" t="n">
         <v>2.25</v>
@@ -1626,7 +1626,7 @@
         <v>1.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
         <v>1.42</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45917.46875</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.16</v>
+        <v>4.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.71</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>2.58</v>
+        <v>1.77</v>
       </c>
       <c r="O10" t="n">
-        <v>2.49</v>
+        <v>4.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.43</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="T10" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
-        <v>5.1</v>
+        <v>2.83</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.07</v>
+        <v>3.82</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>1.19</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.45</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45917.47916666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45917.47916666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
         <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
+        <v>5.3</v>
       </c>
       <c r="O15" t="n">
-        <v>4.75</v>
+        <v>2.42</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.38</v>
+        <v>5.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="X15" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.12</v>
+        <v>2.51</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.82</v>
+        <v>4.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.62</v>
+        <v>3.2</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45917.47916666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45917.47916666666</v>
@@ -3000,25 +3000,25 @@
         <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="T20" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
         <v>1</v>
@@ -3036,16 +3036,16 @@
         <v>2.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45917.54166666666</v>
@@ -3258,34 +3258,34 @@
         <v>2.75</v>
       </c>
       <c r="O22" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="R22" t="n">
         <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
-        <v>3.44</v>
+        <v>3.76</v>
       </c>
       <c r="Y22" t="n">
         <v>1.8</v>
@@ -3294,10 +3294,10 @@
         <v>1.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AC22" t="n">
         <v>1.66</v>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45917.54166666666</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45917.5625</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3645,13 +3645,13 @@
         <v>3.05</v>
       </c>
       <c r="O25" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="P25" t="n">
         <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
         <v>1.32</v>
@@ -3660,19 +3660,19 @@
         <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="U25" t="n">
         <v>1.53</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>3.8</v>
+        <v>4.04</v>
       </c>
       <c r="Y25" t="n">
         <v>1.8</v>
@@ -3687,10 +3687,10 @@
         <v>1.49</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3706,13 +3706,13 @@
         <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45917.5625</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>6.8</v>
+        <v>3.57</v>
       </c>
       <c r="O26" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="P26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q26" t="n">
-        <v>7</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.62</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45917.57291666666</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.57</v>
+        <v>6.8</v>
       </c>
       <c r="O27" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>3.62</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.88</v>
+        <v>2.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45917.57291666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="M28" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N28" t="n">
+        <v>6</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T28" t="n">
         <v>3.3</v>
       </c>
-      <c r="N28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="U28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH28" t="n">
         <v>2.24</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X28" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.36</v>
+        <v>1.89</v>
       </c>
       <c r="M32" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.59</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T32" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="U32" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V32" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X32" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Y32" t="n">
         <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>1.26</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="M34" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>3.11</v>
+        <v>4.25</v>
       </c>
       <c r="O34" t="n">
-        <v>2.61</v>
+        <v>2.26</v>
       </c>
       <c r="P34" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="S34" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="T34" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="U34" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="V34" t="n">
         <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="X34" t="n">
-        <v>4.15</v>
+        <v>3.55</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45917.58333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.78</v>
+        <v>2.88</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>2.58</v>
       </c>
       <c r="N35" t="n">
-        <v>4.25</v>
+        <v>2.6</v>
       </c>
       <c r="O35" t="n">
-        <v>2.26</v>
+        <v>3.45</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="S35" t="n">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="T35" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="X35" t="n">
-        <v>3.55</v>
+        <v>2.3</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.89</v>
+        <v>2.56</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.88</v>
+        <v>4.7</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.52</v>
+        <v>1.99</v>
       </c>
       <c r="M36" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>3.11</v>
       </c>
       <c r="O36" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="P36" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.81</v>
+        <v>3.55</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S36" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="T36" t="n">
-        <v>3.28</v>
+        <v>2.38</v>
       </c>
       <c r="U36" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W36" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="X36" t="n">
-        <v>2.7</v>
+        <v>4.15</v>
       </c>
       <c r="Y36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45917.58333333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="O37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.88</v>
+        <v>1.88</v>
       </c>
       <c r="M39" t="n">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="N39" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="O39" t="n">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="P39" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.7</v>
+        <v>4.03</v>
       </c>
       <c r="R39" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="U39" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="V39" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W39" t="n">
-        <v>1.55</v>
+        <v>1.19</v>
       </c>
       <c r="X39" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.56</v>
+        <v>1.72</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="M40" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3.46</v>
+        <v>2.2</v>
       </c>
       <c r="P40" t="n">
         <v>2.31</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.32</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="T40" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
         <v>1.18</v>
       </c>
       <c r="X40" t="n">
-        <v>4.63</v>
+        <v>4.75</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Z40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA40" t="n">
         <v>2.31</v>
       </c>
-      <c r="AA40" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AB40" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.21</v>
+        <v>1.8</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5838,28 +5838,28 @@
         <v>3.9</v>
       </c>
       <c r="O42" t="n">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="P42" t="n">
         <v>1.82</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="R42" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="S42" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="T42" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="U42" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="V42" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="W42" t="n">
         <v>1.6</v>
@@ -5874,16 +5874,16 @@
         <v>1.3</v>
       </c>
       <c r="AA42" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45917.60416666666</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.3</v>
+        <v>8.5</v>
       </c>
       <c r="M43" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>2.3</v>
+        <v>1.37</v>
       </c>
       <c r="O43" t="n">
-        <v>3.85</v>
+        <v>8.25</v>
       </c>
       <c r="P43" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.59</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="S43" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AI43" t="n">
         <v>3.95</v>
       </c>
-      <c r="U43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45917.60416666666</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="M44" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N44" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="O44" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P44" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.86</v>
+        <v>3.59</v>
       </c>
       <c r="R44" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="S44" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="T44" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="U44" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V44" t="n">
         <v>1.14</v>
       </c>
-      <c r="V44" t="n">
-        <v>1.15</v>
-      </c>
       <c r="W44" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="X44" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Y44" t="n">
-        <v>3.41</v>
+        <v>2.85</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AA44" t="n">
-        <v>7.6</v>
+        <v>6.25</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,16 +6154,16 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45917.60416666666</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.47</v>
+        <v>2.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.78</v>
+        <v>2.7</v>
       </c>
       <c r="N46" t="n">
-        <v>7.8</v>
+        <v>3.05</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.3</v>
+        <v>3.41</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,16 +6412,16 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45917.60416666666</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6507,16 +6507,16 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,16 +6670,16 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45917.625</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -7002,22 +7002,22 @@
         <v>2.23</v>
       </c>
       <c r="P51" t="n">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="Q51" t="n">
         <v>4.3</v>
       </c>
       <c r="R51" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S51" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="T51" t="n">
         <v>2.38</v>
       </c>
       <c r="U51" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V51" t="n">
         <v>1.04</v>
@@ -7026,7 +7026,7 @@
         <v>1.17</v>
       </c>
       <c r="X51" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="Y51" t="n">
         <v>1.68</v>
@@ -7035,7 +7035,7 @@
         <v>2.18</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AB51" t="n">
         <v>1.48</v>
@@ -7044,29 +7044,29 @@
         <v>1.64</v>
       </c>
       <c r="AD51" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH51" t="n">
         <v>2.12</v>
       </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45917.64583333334</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.69</v>
+        <v>6.2</v>
       </c>
       <c r="M52" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N52" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="O52" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.39</v>
+        <v>1.53</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="N53" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="O53" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="P53" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="R53" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S53" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="T53" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="V53" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W53" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X53" t="n">
-        <v>4.55</v>
+        <v>5.6</v>
       </c>
